--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 11-Sep-2026  14:53:26    |    Closing Price Date: 11-Sep-2026</t>
+          <t>Scan Run: 14-Sep-2026  16:49:26    |    Closing Price Date: 11-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>34.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>11-Sep-2026  14:53:26</t>
+          <t>14-Sep-2026  16:49:26</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.6% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 48.4% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 243 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 242 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1876.92</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1692.54</v>
+        <v>1692.2</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>734.48</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>805.42</v>
+        <v>806.17</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>1116.61</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1228.65</v>
+        <v>1229.51</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>559.89</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>484.69</v>
+        <v>484.48</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1404.33</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1364.96</v>
+        <v>1365.1</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>331.78</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>278.87</v>
+        <v>279.6</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>3254.1</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>3246.84</v>
+        <v>3248.21</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1304.05</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1352.81</v>
+        <v>1353.84</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>432.83</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>393.53</v>
+        <v>394.02</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>1427.83</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>1128.45</v>
+        <v>1128.95</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>2709.26</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2908.89</v>
+        <v>2905.82</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>275.02</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>297.61</v>
+        <v>297.68</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>4101.17</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>3725.9</v>
+        <v>3725.21</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>2288.58</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2478.29</v>
+        <v>2479.92</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>7741.17</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7259.23</v>
+        <v>7262.14</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1888.21</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>1891.53</v>
+        <v>1891.12</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>1051.74</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>989.38</v>
+        <v>991.9299999999999</v>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>178.84</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>197.44</v>
+        <v>197.61</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>307.95</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>282.84</v>
+        <v>283.3</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>1761.08</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1584.45</v>
+        <v>1587.27</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>414.3</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>413.46</v>
+        <v>413.7</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>2283.52</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>2283.81</v>
+        <v>2285.12</v>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>602.54</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>775.9400000000001</v>
+        <v>777.37</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1722.55</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1637.26</v>
+        <v>1638.52</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>13361.94</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>13695.67</v>
+        <v>13714.87</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>1262.79</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1266.83</v>
+        <v>1268.88</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>3993.42</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3930.03</v>
+        <v>3932.17</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1930,9 +1930,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
@@ -1962,7 +1962,7 @@
         <v>3614.19</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3985.93</v>
+        <v>3982.45</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>5350.88</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5170.68</v>
+        <v>5176.55</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>1033.43</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1006.02</v>
+        <v>1006.57</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>1562.42</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1495.6</v>
+        <v>1496.48</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>5425.28</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5333.65</v>
+        <v>5345.33</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>2621.86</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2566.16</v>
+        <v>2566.12</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>408.09</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>412.74</v>
+        <v>412.81</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>759.71</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>630.29</v>
+        <v>629.62</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>407.01</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>466.88</v>
+        <v>467.26</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>3477.66</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3332.72</v>
+        <v>3340.88</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>13849.69</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>13071.86</v>
+        <v>13070.26</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1444.22</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1367.37</v>
+        <v>1367.73</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1061.26</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>970.78</v>
+        <v>973.08</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         <v>396.84</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>383.1</v>
+        <v>383.11</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>340.61</v>
+        <v>341.36</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2054.23</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2181.48</v>
+        <v>2182.64</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>48.47</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>51.61</v>
+        <v>51.63</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>274.2</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>304.4</v>
+        <v>304.64</v>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>8371.35</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>7171.97</v>
+        <v>7172.62</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1274.26</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1316.2</v>
+        <v>1317.07</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1170.83</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1086.67</v>
+        <v>1089.42</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>402.98</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>399.01</v>
+        <v>399.77</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>170.53</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>163.51</v>
+        <v>163.57</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>317.91</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>312.48</v>
+        <v>312.22</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>4417.01</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4044.03</v>
+        <v>4041.67</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>1904.1</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1817.78</v>
+        <v>1818.98</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>302.21</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>293.24</v>
+        <v>293.53</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>201.07</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>183.01</v>
+        <v>183.22</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>1757.38</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1369.73</v>
+        <v>1371.56</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>1013.08</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>953.54</v>
+        <v>954.16</v>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>3925.57</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4053.86</v>
+        <v>4058.13</v>
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>219.07</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>156.38</v>
+        <v>156.47</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>2996.94</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2700.83</v>
+        <v>2704.66</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>4880.39</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4417.94</v>
+        <v>4419.73</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>241.46</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>253.92</v>
+        <v>254.5</v>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>4882.7</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>4395</v>
+        <v>4396.38</v>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>1322.24</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1070.69</v>
+        <v>1070.59</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>17986.78</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>18567.75</v>
+        <v>18560.36</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>3050.34</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2665.93</v>
+        <v>2674.83</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>1509.37</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1278.46</v>
+        <v>1279.69</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>210.56</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>190.25</v>
+        <v>190.4</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         <v>32575.39</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>32936.9</v>
+        <v>32936.89</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>29173.63</v>
+        <v>29104.73</v>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>890.2</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>819.53</v>
+        <v>819.72</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>11456.72</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>11500.35</v>
+        <v>11509.4</v>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>339.31</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>348.45</v>
+        <v>348.76</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>1097.59</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1113.83</v>
+        <v>1118.52</v>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>11396.3</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>10218.35</v>
+        <v>10221.42</v>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>378.01</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>393.29</v>
+        <v>394.31</v>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>1454.56</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1383.5</v>
+        <v>1381.64</v>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
@@ -4115,10 +4115,10 @@
         <v>8733.1</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>8956.700000000001</v>
+        <v>8956.709999999999</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>8440.290000000001</v>
+        <v>8450.33</v>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>340.23</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>311.69</v>
+        <v>313.02</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>439.81</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>464.21</v>
+        <v>464.57</v>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>1424.21</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1032.27</v>
+        <v>1032.51</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>4339.82</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>3651.79</v>
+        <v>3648.77</v>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>421.68</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>408.3</v>
+        <v>409.44</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>95.22</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>96.23</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>2989.48</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>3140.39</v>
+        <v>3151.34</v>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>14.1</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>12.18</v>
+        <v>12.19</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>147.69</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>142.51</v>
+        <v>142.52</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>5108.4</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>5020.34</v>
+        <v>5032.1</v>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>326.39</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>286.47</v>
+        <v>286.76</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>1783.92</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1846.67</v>
+        <v>1847.29</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>239.95</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>249.03</v>
+        <v>249.21</v>
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>4756.23</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>4518.75</v>
+        <v>4520.71</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>4877.94</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>4077.24</v>
+        <v>4075.7</v>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>2471.48</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2532.85</v>
+        <v>2531.03</v>
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>2244.33</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2227.47</v>
+        <v>2229.51</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>187.8</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>187.38</v>
+        <v>187.5</v>
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>693.25</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>605.04</v>
+        <v>605.65</v>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>284.12</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>400.01</v>
+        <v>400.82</v>
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>2832.17</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2435.55</v>
+        <v>2439.49</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>11458.78</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>9721</v>
+        <v>9740.67</v>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>43.7</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>7345.08</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>6629.82</v>
+        <v>6636.98</v>
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>2914.21</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>3206.73</v>
+        <v>3223.44</v>
       </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>549.11</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>616.27</v>
+        <v>616.34</v>
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>402.81</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>440.53</v>
+        <v>440.28</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>2379.69</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>2383.64</v>
+        <v>2387.61</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>81.89</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>69.87</v>
+        <v>69.86</v>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>366.55</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>378.05</v>
+        <v>378.13</v>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>415.05</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>354.97</v>
+        <v>355.15</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>8741.66</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>8148.37</v>
+        <v>8151.55</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>167.68</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>161.6</v>
+        <v>161.75</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>380.6</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>389.98</v>
+        <v>390.47</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>604.62</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>539.4299999999999</v>
+        <v>541.88</v>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>1604.36</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1460.34</v>
+        <v>1458.65</v>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>246.07</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>257.62</v>
+        <v>257.7</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>1520.94</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1327.74</v>
+        <v>1329.2</v>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>274.65</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>282.99</v>
+        <v>283.47</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>1019.16</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>989.61</v>
+        <v>989.79</v>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>4532.15</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>3873.47</v>
+        <v>3872.05</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>2825.14</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>2855.55</v>
+        <v>2853.94</v>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>343.29</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>302.28</v>
+        <v>302.36</v>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>364.37</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>332.34</v>
+        <v>333.18</v>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>374.97</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>349.1</v>
+        <v>349.28</v>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>4398.27</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>4566.12</v>
+        <v>4570.38</v>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>1817.94</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1697.74</v>
+        <v>1703.24</v>
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>381.28</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>322.21</v>
+        <v>321.98</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>411.76</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>397.83</v>
+        <v>397.9</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>313</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>316.38</v>
+        <v>316.72</v>
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1456.57</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1392.94</v>
+        <v>1393.28</v>
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>153.65</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>137.72</v>
+        <v>137.8</v>
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>1218.93</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1281.27</v>
+        <v>1283.09</v>
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>326.79</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>378.33</v>
+        <v>378.69</v>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>266.04</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>274.25</v>
+        <v>274.01</v>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>180.18</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>167.32</v>
+        <v>167.4</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>780.63</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>705.8200000000001</v>
+        <v>706.48</v>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>16048.14</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>12890.82</v>
+        <v>12900.69</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131.31</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>128.89</v>
+        <v>129.14</v>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>2702.88</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>2225.92</v>
+        <v>2226.86</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>361.07</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>437.07</v>
+        <v>437.35</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>1062.36</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1103.88</v>
+        <v>1103.76</v>
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>598.97</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>562.24</v>
+        <v>562.85</v>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1037.73</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1056.88</v>
+        <v>1058.8</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>1609.62</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1525.72</v>
+        <v>1524.93</v>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>5396.53</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>5416.87</v>
+        <v>5417.09</v>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>597.51</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>559.26</v>
+        <v>559.17</v>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>127.51</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>129.17</v>
+        <v>129.18</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>836.24</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>798.0700000000001</v>
+        <v>798.13</v>
       </c>
       <c r="G151" s="14" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>720.2</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>702.98</v>
+        <v>703.36</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>5225.94</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>4870.76</v>
+        <v>4878.35</v>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>1579.98</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1532.08</v>
+        <v>1537.27</v>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>1348.73</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1245.21</v>
+        <v>1246.43</v>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>83.42</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>77.51000000000001</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>19755.49</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>17086.37</v>
+        <v>17087.15</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>176.92</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>176.99</v>
+        <v>177.69</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>19.71</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>20.75</v>
+        <v>20.79</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>329.61</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>301.95</v>
+        <v>302.94</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>5296.7</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>4968.56</v>
+        <v>4971.21</v>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>179.31</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>167.97</v>
+        <v>168.06</v>
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>578.16</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>559.41</v>
+        <v>561.67</v>
       </c>
       <c r="G163" s="14" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>10385.3</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>8718.33</v>
+        <v>8719.58</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>1191.8</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>1235.89</v>
+        <v>1238.6</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>656.14</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>647.6</v>
+        <v>650.65</v>
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>334.79</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>344.9</v>
+        <v>345.87</v>
       </c>
       <c r="G167" s="14" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>572.35</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>527.76</v>
+        <v>527.74</v>
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>883.15</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>878.98</v>
+        <v>879.51</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>2126.47</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>2058.66</v>
+        <v>2063.66</v>
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>1143.21</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>1108.63</v>
+        <v>1110.33</v>
       </c>
       <c r="G171" s="14" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>1947.5</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1909.27</v>
+        <v>1911.81</v>
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>37288.91</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>37872.47</v>
+        <v>37871.95</v>
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>5285.79</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>5444.11</v>
+        <v>5450.32</v>
       </c>
       <c r="G174" s="14" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>77.48999999999999</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>97.34999999999999</v>
+        <v>97.34</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>87.16</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>100.02</v>
+        <v>100.11</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>3457.14</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>3093.13</v>
+        <v>3093.49</v>
       </c>
       <c r="G177" s="14" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>158.16</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>136.89</v>
+        <v>137.11</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>587.4400000000001</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>573.13</v>
+        <v>573.15</v>
       </c>
       <c r="G179" s="14" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>3673.95</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>4273.21</v>
+        <v>4280.61</v>
       </c>
       <c r="G180" s="14" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>2566.15</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>2031.6</v>
+        <v>2031.93</v>
       </c>
       <c r="G181" s="14" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>1549.73</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>1597.36</v>
+        <v>1598.15</v>
       </c>
       <c r="G182" s="14" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>7434.78</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>7369.58</v>
+        <v>7386.21</v>
       </c>
       <c r="G183" s="14" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1060.51</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>987.75</v>
+        <v>989.7</v>
       </c>
       <c r="G184" s="14" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>1938.63</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>2050.19</v>
+        <v>2048.96</v>
       </c>
       <c r="G185" s="14" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>219.67</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>201.67</v>
+        <v>201.88</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>463.08</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>451.06</v>
+        <v>451.17</v>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>540.36</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>567.84</v>
+        <v>568.77</v>
       </c>
       <c r="G188" s="14" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>22.77</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>22.13</v>
+        <v>22.12</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>1251.58</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1183.5</v>
+        <v>1187.93</v>
       </c>
       <c r="G190" s="14" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>994.45</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>926.52</v>
+        <v>927.4400000000001</v>
       </c>
       <c r="G191" s="14" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>1416.09</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>1403.78</v>
+        <v>1405.19</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>8127.02</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>6999.91</v>
+        <v>6999.09</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>2108.26</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>2272.32</v>
+        <v>2271.26</v>
       </c>
       <c r="G194" s="14" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>3247.43</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2691.38</v>
+        <v>2691.57</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>17.14</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>17.4</v>
+        <v>17.49</v>
       </c>
       <c r="G196" s="14" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>1724.42</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>1678.17</v>
+        <v>1680.79</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>922.54</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>946.13</v>
+        <v>949.48</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>1286.91</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>1225.22</v>
+        <v>1226.83</v>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>1607.4</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>1428.54</v>
+        <v>1429.47</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>1839.79</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>1636.48</v>
+        <v>1637.11</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>113.52</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>110.94</v>
+        <v>111.05</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45131.1</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>39658.11</v>
+        <v>39669.34</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>524.9400000000001</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>490.74</v>
+        <v>490.97</v>
       </c>
       <c r="G205" s="14" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>794.13</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>885.28</v>
+        <v>889.5700000000001</v>
       </c>
       <c r="G206" s="14" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>416.8</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>457.9</v>
+        <v>458.21</v>
       </c>
       <c r="G207" s="14" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>1972.55</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>1926.18</v>
+        <v>1934.5</v>
       </c>
       <c r="G208" s="14" t="inlineStr">
         <is>
@@ -9879,10 +9879,10 @@
         <v>1491.8</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>1481.07</v>
+        <v>1481.08</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>1544.01</v>
+        <v>1552.65</v>
       </c>
       <c r="G209" s="14" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>85.3</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>82.77</v>
+        <v>82.92</v>
       </c>
       <c r="G210" s="14" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>1355.04</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1361.08</v>
+        <v>1364.83</v>
       </c>
       <c r="G211" s="14" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>21417.63</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>17590.25</v>
+        <v>17628.33</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>2588.08</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>2629.97</v>
+        <v>2626.43</v>
       </c>
       <c r="G213" s="14" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>1282.35</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>1043.37</v>
+        <v>1043.41</v>
       </c>
       <c r="G214" s="14" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>475.73</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>546.87</v>
+        <v>548.17</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>374.59</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>386.09</v>
+        <v>386.6</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>520.99</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>591.62</v>
+        <v>591.83</v>
       </c>
       <c r="G217" s="14" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>2339.76</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>2180.86</v>
+        <v>2184.38</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>293.33</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>298.79</v>
+        <v>298.88</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>172.88</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>168.78</v>
+        <v>168.95</v>
       </c>
       <c r="G220" s="14" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>138.38</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>142.91</v>
+        <v>143.02</v>
       </c>
       <c r="G221" s="14" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>55.87</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>63.25</v>
+        <v>63.27</v>
       </c>
       <c r="G222" s="14" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>1852.98</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>1655.38</v>
+        <v>1655.07</v>
       </c>
       <c r="G223" s="14" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>780.8</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>740.61</v>
+        <v>740.05</v>
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>575.58</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>572.5700000000001</v>
+        <v>572.96</v>
       </c>
       <c r="G225" s="14" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>101.6</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>99.76000000000001</v>
+        <v>99.86</v>
       </c>
       <c r="G226" s="14" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>2619.26</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>2713.35</v>
+        <v>2716.61</v>
       </c>
       <c r="G227" s="14" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>1120.97</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>1015.2</v>
+        <v>1018.04</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>3226.12</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>3002.17</v>
+        <v>3004.61</v>
       </c>
       <c r="G229" s="14" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>1459.89</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1378.5</v>
+        <v>1379.94</v>
       </c>
       <c r="G230" s="14" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>1919.46</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>1817.65</v>
+        <v>1818.82</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>2044.21</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1935.79</v>
+        <v>1935.3</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>1125.71</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1037.8</v>
+        <v>1039.51</v>
       </c>
       <c r="G234" s="14" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>310.4</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>287.15</v>
+        <v>287.87</v>
       </c>
       <c r="G235" s="14" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>1482.27</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>1494.62</v>
+        <v>1495.14</v>
       </c>
       <c r="G236" s="14" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>707.79</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>657.2</v>
+        <v>656.5599999999999</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>38.92</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>39</v>
+        <v>38.97</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>527.77</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>531.54</v>
+        <v>532.3</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>1953.3</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>1709.31</v>
+        <v>1710.02</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>298.98</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>334.89</v>
+        <v>335.48</v>
       </c>
       <c r="G243" s="14" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>962.3200000000001</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>888.62</v>
+        <v>891.49</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>3871.69</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>3567.47</v>
+        <v>3570.58</v>
       </c>
       <c r="G245" s="14" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>1245.86</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>1312.25</v>
+        <v>1314.58</v>
       </c>
       <c r="G246" s="14" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>2401.87</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>2356.09</v>
+        <v>2356.54</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>1215.44</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>1169.9</v>
+        <v>1171.46</v>
       </c>
       <c r="G248" s="14" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>2559.25</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>2576.31</v>
+        <v>2587.8</v>
       </c>
       <c r="G249" s="14" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>142.46</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>140.38</v>
+        <v>140.55</v>
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>330.66</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>294.88</v>
+        <v>295.14</v>
       </c>
       <c r="G251" s="14" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>468.75</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>453.19</v>
+        <v>453.56</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>285.01</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>284.18</v>
+        <v>284.34</v>
       </c>
       <c r="G253" s="14" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>1123.34</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>1112.65</v>
+        <v>1113.6</v>
       </c>
       <c r="G255" s="14" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>1736.33</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>1697.3</v>
+        <v>1697.24</v>
       </c>
       <c r="G256" s="14" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>644.5599999999999</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>697.8099999999999</v>
+        <v>700.9299999999999</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>1622.28</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>1758.2</v>
+        <v>1764.6</v>
       </c>
       <c r="G258" s="14" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>1328.96</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>1388.02</v>
+        <v>1387.74</v>
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>1293.32</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>1367.37</v>
+        <v>1367.42</v>
       </c>
       <c r="G260" s="14" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>413.95</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>414.92</v>
+        <v>415.11</v>
       </c>
       <c r="G261" s="14" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>1173.34</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>1042.08</v>
+        <v>1044.44</v>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>570.03</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>548.54</v>
+        <v>547.3099999999999</v>
       </c>
       <c r="G263" s="14" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>2053.08</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>1849.05</v>
+        <v>1852.11</v>
       </c>
       <c r="G264" s="14" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>861.87</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>830.64</v>
+        <v>831.37</v>
       </c>
       <c r="G265" s="14" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>223.91</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>269.01</v>
+        <v>269.09</v>
       </c>
       <c r="G266" s="14" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>122.38</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>129.41</v>
+        <v>129.7</v>
       </c>
       <c r="G267" s="14" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>843.62</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>728.91</v>
+        <v>729.29</v>
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>7531.56</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>7961.73</v>
+        <v>7954.73</v>
       </c>
       <c r="G269" s="14" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>215.36</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>214.62</v>
+        <v>215.03</v>
       </c>
       <c r="G270" s="14" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>84.94</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>90.23</v>
+        <v>90.45</v>
       </c>
       <c r="G271" s="14" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>82.29000000000001</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>74.51000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>500.47</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>543.27</v>
+        <v>543.03</v>
       </c>
       <c r="G273" s="14" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>508.77</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>482.15</v>
+        <v>482.85</v>
       </c>
       <c r="G274" s="14" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>545.8200000000001</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>534.23</v>
+        <v>535.38</v>
       </c>
       <c r="G275" s="14" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>503.37</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>504.05</v>
+        <v>503.98</v>
       </c>
       <c r="G276" s="14" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>2142.05</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>1755.9</v>
+        <v>1757.45</v>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>242.87</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>209.69</v>
+        <v>210.95</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>109.18</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>118.09</v>
+        <v>118.29</v>
       </c>
       <c r="G279" s="14" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>36411.25</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>35232.95</v>
+        <v>35220.15</v>
       </c>
       <c r="G280" s="14" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>960.02</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>1050.14</v>
+        <v>1049.76</v>
       </c>
       <c r="G281" s="14" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>2802.94</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>2655.47</v>
+        <v>2657.25</v>
       </c>
       <c r="G282" s="14" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>85.14</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>86.64</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="G283" s="14" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>247.05</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>262.64</v>
+        <v>262.92</v>
       </c>
       <c r="G284" s="14" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>682.74</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>606.03</v>
+        <v>609.09</v>
       </c>
       <c r="G285" s="14" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>785.92</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>725.59</v>
+        <v>725.02</v>
       </c>
       <c r="G286" s="14" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>1788.24</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>1677.07</v>
+        <v>1668.09</v>
       </c>
       <c r="G287" s="14" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>1254.17</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>984.73</v>
+        <v>984.89</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>903.36</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>954.33</v>
+        <v>956</v>
       </c>
       <c r="G289" s="14" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>233.21</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>206.61</v>
+        <v>206.87</v>
       </c>
       <c r="G290" s="14" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>540.8200000000001</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>518.17</v>
+        <v>518.8099999999999</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>1554.45</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>1636</v>
+        <v>1642.66</v>
       </c>
       <c r="G292" s="14" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>4075.3</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>3923.96</v>
+        <v>3925.93</v>
       </c>
       <c r="G293" s="14" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>284.15</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>279.35</v>
+        <v>279.48</v>
       </c>
       <c r="G294" s="14" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>90.83</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>97.66</v>
+        <v>97.81</v>
       </c>
       <c r="G295" s="14" t="inlineStr">
         <is>
@@ -13707,10 +13707,10 @@
         <v>130810.79</v>
       </c>
       <c r="E296" s="11" t="n">
-        <v>131426.4</v>
+        <v>131426.41</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>134898.75</v>
+        <v>134999.81</v>
       </c>
       <c r="G296" s="14" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>526.97</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>515.28</v>
+        <v>520.04</v>
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>1591.74</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>1587.45</v>
+        <v>1590.23</v>
       </c>
       <c r="G298" s="14" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>77.12</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>78.20999999999999</v>
+        <v>78.37</v>
       </c>
       <c r="G299" s="14" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>471.8</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>492.7</v>
+        <v>493.23</v>
       </c>
       <c r="G300" s="14" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>758.61</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>754.77</v>
+        <v>755.5599999999999</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>1264.7</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>1121.32</v>
+        <v>1121.86</v>
       </c>
       <c r="G303" s="14" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>579.76</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>577.35</v>
+        <v>579.1799999999999</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>1023.22</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>937.64</v>
+        <v>938.76</v>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>156.46</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>154.41</v>
+        <v>154.55</v>
       </c>
       <c r="G306" s="14" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>641.65</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>637.8</v>
+        <v>638.7</v>
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>91.84</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>96.39</v>
+        <v>96.58</v>
       </c>
       <c r="G308" s="14" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>899.24</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>856.27</v>
+        <v>853.41</v>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>584.42</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>626.62</v>
+        <v>626.48</v>
       </c>
       <c r="G310" s="14" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>398.58</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>361.44</v>
+        <v>362.07</v>
       </c>
       <c r="G311" s="14" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>3505.61</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>3616.84</v>
+        <v>3621.51</v>
       </c>
       <c r="G312" s="14" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>1358.4</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>1165.94</v>
+        <v>1165.12</v>
       </c>
       <c r="G313" s="14" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>11052.88</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>10979.47</v>
+        <v>11013.24</v>
       </c>
       <c r="G314" s="14" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>1363.99</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>1313.2</v>
+        <v>1313.07</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>964.48</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>976.77</v>
+        <v>975.72</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>1149.43</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>1066.75</v>
+        <v>1064.77</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>1421.4</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>1163.26</v>
+        <v>1164.71</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>1819.36</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>1773.03</v>
+        <v>1776.05</v>
       </c>
       <c r="G319" s="14" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>705.12</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>780.58</v>
+        <v>778.76</v>
       </c>
       <c r="G320" s="14" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>3475.95</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>3514.3</v>
+        <v>3521.41</v>
       </c>
       <c r="G321" s="14" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>2067.78</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>1439.39</v>
+        <v>1441.15</v>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>464.17</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>446.8</v>
+        <v>448.02</v>
       </c>
       <c r="G323" s="14" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>1555.39</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>1664.76</v>
+        <v>1665.47</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>117.32</v>
       </c>
       <c r="F325" s="11" t="n">
-        <v>127.07</v>
+        <v>127.45</v>
       </c>
       <c r="G325" s="14" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>4469.07</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>3925.92</v>
+        <v>3924.61</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>650.1900000000001</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>639.7</v>
+        <v>640.05</v>
       </c>
       <c r="G327" s="14" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>446.99</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>553.35</v>
+        <v>555.01</v>
       </c>
       <c r="G328" s="14" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>163.69</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>173.69</v>
+        <v>173.9</v>
       </c>
       <c r="G329" s="14" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>599.87</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>622.55</v>
+        <v>622.4400000000001</v>
       </c>
       <c r="G330" s="14" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>2554.46</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>2912.25</v>
+        <v>2910.88</v>
       </c>
       <c r="G331" s="14" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>1791.29</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>1983.19</v>
+        <v>1988.88</v>
       </c>
       <c r="G332" s="14" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>269.42</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>302.93</v>
+        <v>303.53</v>
       </c>
       <c r="G333" s="14" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>1400</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>1279.04</v>
+        <v>1279.1</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>1804.9</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>1889.15</v>
+        <v>1891.7</v>
       </c>
       <c r="G335" s="14" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>6510.1</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>6494.79</v>
+        <v>6506.94</v>
       </c>
       <c r="G336" s="14" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>109.59</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>120.86</v>
+        <v>120.93</v>
       </c>
       <c r="G337" s="14" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>1755.31</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>1728.58</v>
+        <v>1731.09</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>1358.56</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>1418.9</v>
+        <v>1420.19</v>
       </c>
       <c r="G339" s="12" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>926.7</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>917.42</v>
+        <v>918.59</v>
       </c>
       <c r="G340" s="14" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>1825.71</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>1728.61</v>
+        <v>1733.8</v>
       </c>
       <c r="G341" s="14" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>713.79</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>746.5700000000001</v>
+        <v>746.42</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>2523.89</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>2436.33</v>
+        <v>2439.1</v>
       </c>
       <c r="G343" s="14" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>2109.54</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>1809.46</v>
+        <v>1809.72</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>460.23</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>386.78</v>
+        <v>386.95</v>
       </c>
       <c r="G345" s="14" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>556.6</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>527.99</v>
+        <v>528.01</v>
       </c>
       <c r="G346" s="14" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>3475.23</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>3604.51</v>
+        <v>3605.31</v>
       </c>
       <c r="G347" s="14" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>997.4</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>1140.48</v>
+        <v>1140.82</v>
       </c>
       <c r="G348" s="14" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>23.35</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>29.2</v>
+        <v>29.35</v>
       </c>
       <c r="G349" s="14" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>1306.62</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>1277.18</v>
+        <v>1277.02</v>
       </c>
       <c r="G350" s="14" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>1581.85</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>1635.94</v>
+        <v>1635.28</v>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>24703.72</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>25733</v>
+        <v>25748.79</v>
       </c>
       <c r="G353" s="14" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>1212.06</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>1135.4</v>
+        <v>1135.72</v>
       </c>
       <c r="G354" s="14" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>38.66</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>40.11</v>
+        <v>40.2</v>
       </c>
       <c r="G356" s="14" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>252.21</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>279.43</v>
+        <v>279.76</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>434.23</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>451.92</v>
+        <v>451.64</v>
       </c>
       <c r="G359" s="14" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>494.09</v>
       </c>
       <c r="F361" s="11" t="n">
-        <v>556.78</v>
+        <v>557.22</v>
       </c>
       <c r="G361" s="14" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>290.5</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>271.91</v>
+        <v>272.09</v>
       </c>
       <c r="G362" s="14" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>695.95</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>622.1799999999999</v>
+        <v>624.3099999999999</v>
       </c>
       <c r="G363" s="14" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>1079.87</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>1005.29</v>
+        <v>1005.18</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>1843.18</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>1637.5</v>
+        <v>1636.4</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>285.26</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>254.83</v>
+        <v>255.09</v>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>430.56</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>438.06</v>
+        <v>438.64</v>
       </c>
       <c r="G368" s="14" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>285.29</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>320.83</v>
+        <v>321.91</v>
       </c>
       <c r="G369" s="14" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>502.34</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>463.76</v>
+        <v>463.86</v>
       </c>
       <c r="G370" s="14" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>1901.99</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>1866.41</v>
+        <v>1868.56</v>
       </c>
       <c r="G372" s="14" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>5257.96</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>5465.98</v>
+        <v>5473.86</v>
       </c>
       <c r="G373" s="14" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>1909.21</v>
       </c>
       <c r="F374" s="11" t="n">
-        <v>1850.1</v>
+        <v>1849.84</v>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>302.71</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>347.38</v>
+        <v>348.1</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>1320.49</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>1461.47</v>
+        <v>1462.64</v>
       </c>
       <c r="G376" s="14" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>4390.65</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>4134.55</v>
+        <v>4133.53</v>
       </c>
       <c r="G377" s="14" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>1411.62</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>1347.66</v>
+        <v>1353.34</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>892.86</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>930.55</v>
+        <v>930.73</v>
       </c>
       <c r="G379" s="14" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>155.31</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>159.17</v>
+        <v>159.22</v>
       </c>
       <c r="G380" s="14" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>853.8099999999999</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>838.6900000000001</v>
+        <v>839.09</v>
       </c>
       <c r="G381" s="14" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>1754.71</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>1575.38</v>
+        <v>1577.67</v>
       </c>
       <c r="G382" s="14" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>1124.28</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>1073.07</v>
+        <v>1072.38</v>
       </c>
       <c r="G383" s="14" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>1185.46</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>1159.93</v>
+        <v>1160.91</v>
       </c>
       <c r="G384" s="14" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>248.29</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>253.99</v>
+        <v>253.91</v>
       </c>
       <c r="G385" s="14" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>1341.47</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>1471.4</v>
+        <v>1473.76</v>
       </c>
       <c r="G386" s="14" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>2558.4</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>2222.29</v>
+        <v>2217.78</v>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>726.46</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>730.46</v>
+        <v>732.95</v>
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>486.29</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>486.44</v>
+        <v>486.92</v>
       </c>
       <c r="G389" s="14" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>611.09</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>566.76</v>
+        <v>567.8099999999999</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>190.96</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>203.79</v>
+        <v>203.75</v>
       </c>
       <c r="G391" s="14" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>383.09</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>403.85</v>
+        <v>404.26</v>
       </c>
       <c r="G392" s="14" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>1452.55</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>1379.82</v>
+        <v>1380.54</v>
       </c>
       <c r="G393" s="14" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>1030.99</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>1085.39</v>
+        <v>1086.4</v>
       </c>
       <c r="G394" s="14" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>338.09</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>342.89</v>
+        <v>342.75</v>
       </c>
       <c r="G395" s="14" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>4045.94</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>4037.15</v>
+        <v>4037.46</v>
       </c>
       <c r="G396" s="14" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>25.6</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>26.9</v>
+        <v>26.87</v>
       </c>
       <c r="G397" s="14" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>272.73</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>246.3</v>
+        <v>245.96</v>
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>1699.98</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>1681.27</v>
+        <v>1679.77</v>
       </c>
       <c r="G399" s="14" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>304.75</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>328.38</v>
+        <v>327.72</v>
       </c>
       <c r="G400" s="14" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>658.27</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>719.13</v>
+        <v>720.95</v>
       </c>
       <c r="G401" s="14" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>778.36</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>751.78</v>
+        <v>752.17</v>
       </c>
       <c r="G402" s="14" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>653.3200000000001</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>670.47</v>
+        <v>671.63</v>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>1988.29</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>2061.01</v>
+        <v>2064.37</v>
       </c>
       <c r="G404" s="14" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>1244.9</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>1245.53</v>
+        <v>1246.72</v>
       </c>
       <c r="G405" s="14" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>595.76</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>580.15</v>
+        <v>580.83</v>
       </c>
       <c r="G406" s="14" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>794.61</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>879.46</v>
+        <v>881.65</v>
       </c>
       <c r="G407" s="14" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>2732.65</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>2570.12</v>
+        <v>2569.19</v>
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>249.66</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>229.5</v>
+        <v>229.49</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>184.46</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>181.87</v>
+        <v>181.98</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>285.12</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>314.05</v>
+        <v>314.7</v>
       </c>
       <c r="G411" s="14" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>1110.52</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>1038.89</v>
+        <v>1038.24</v>
       </c>
       <c r="G413" s="14" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>1004.63</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>1106.65</v>
+        <v>1106.91</v>
       </c>
       <c r="G414" s="14" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>504.44</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>504.06</v>
+        <v>504.14</v>
       </c>
       <c r="G415" s="14" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>393.1</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>438.96</v>
+        <v>438.32</v>
       </c>
       <c r="G416" s="14" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>605.89</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>599.92</v>
+        <v>601.13</v>
       </c>
       <c r="G418" s="14" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>644.11</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>562.65</v>
+        <v>563.48</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>494.84</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>446.71</v>
+        <v>446.57</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>281.54</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>238.65</v>
+        <v>239.34</v>
       </c>
       <c r="G421" s="12" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>144.78</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>155.89</v>
+        <v>156.06</v>
       </c>
       <c r="G422" s="14" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>730.17</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>707.22</v>
+        <v>707.64</v>
       </c>
       <c r="G423" s="12" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>4568.9</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>4668.43</v>
+        <v>4669.87</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>6697.48</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>6797.11</v>
+        <v>6795.04</v>
       </c>
       <c r="G425" s="14" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>444.7</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>480.56</v>
+        <v>479.78</v>
       </c>
       <c r="G426" s="14" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>844.4299999999999</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>825.3200000000001</v>
+        <v>826.3099999999999</v>
       </c>
       <c r="G427" s="14" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>127.45</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>131.21</v>
+        <v>132.18</v>
       </c>
       <c r="G428" s="14" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>186.24</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>171.63</v>
+        <v>171.89</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>1645.89</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>1700.21</v>
+        <v>1700.47</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>4638.5</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>4747.77</v>
+        <v>4742.01</v>
       </c>
       <c r="G431" s="14" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>381.87</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>402.78</v>
+        <v>403.11</v>
       </c>
       <c r="G433" s="12" t="inlineStr">
         <is>
@@ -19779,10 +19779,10 @@
         <v>1269.22</v>
       </c>
       <c r="E434" s="11" t="n">
-        <v>1317.03</v>
+        <v>1317.04</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>1388.23</v>
+        <v>1394.06</v>
       </c>
       <c r="G434" s="14" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>495.53</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>459.34</v>
+        <v>459.75</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>153.16</v>
       </c>
       <c r="F436" s="11" t="n">
-        <v>165.75</v>
+        <v>165.98</v>
       </c>
       <c r="G436" s="12" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>1550.84</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>1585.74</v>
+        <v>1582.23</v>
       </c>
       <c r="G437" s="14" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>3006.82</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>3123.88</v>
+        <v>3125.44</v>
       </c>
       <c r="G438" s="14" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>776.91</v>
       </c>
       <c r="F439" s="11" t="n">
-        <v>837.6900000000001</v>
+        <v>837.28</v>
       </c>
       <c r="G439" s="14" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>678.04</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>754.97</v>
+        <v>754.83</v>
       </c>
       <c r="G440" s="14" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>803.0599999999999</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>848.29</v>
+        <v>848.78</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>248.03</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>274.63</v>
+        <v>273.63</v>
       </c>
       <c r="G442" s="14" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>698.5</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>684.9</v>
+        <v>683.91</v>
       </c>
       <c r="G443" s="14" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>1185.12</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>1018.01</v>
+        <v>1018.7</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>20148.84</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>17993.73</v>
+        <v>17978.74</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>1198.47</v>
       </c>
       <c r="F446" s="11" t="n">
-        <v>1128.96</v>
+        <v>1135.97</v>
       </c>
       <c r="G446" s="14" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>283.99</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>327.75</v>
+        <v>327.96</v>
       </c>
       <c r="G447" s="14" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>444.62</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>492.51</v>
+        <v>492.69</v>
       </c>
       <c r="G448" s="14" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>1361.48</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>1270.36</v>
+        <v>1271.11</v>
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>512.61</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>516.17</v>
+        <v>516.63</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>261.89</v>
       </c>
       <c r="F451" s="11" t="n">
-        <v>267.66</v>
+        <v>268.51</v>
       </c>
       <c r="G451" s="14" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>1374.16</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>1447.43</v>
+        <v>1460.72</v>
       </c>
       <c r="G452" s="14" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>482.42</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>525.37</v>
+        <v>525.1900000000001</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>95.17</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>96.45999999999999</v>
+        <v>96.45</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>180.1</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>151.93</v>
+        <v>152.07</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>26460.91</v>
       </c>
       <c r="F456" s="11" t="n">
-        <v>26937.88</v>
+        <v>26958.44</v>
       </c>
       <c r="G456" s="14" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>38.87</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>44.05</v>
+        <v>44.02</v>
       </c>
       <c r="G457" s="14" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>571.35</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>582.72</v>
+        <v>582.6799999999999</v>
       </c>
       <c r="G458" s="14" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>1772.23</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>1679.1</v>
+        <v>1680.83</v>
       </c>
       <c r="G459" s="14" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>821.78</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>837.71</v>
+        <v>838.8</v>
       </c>
       <c r="G460" s="14" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>1703.82</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>1666.69</v>
+        <v>1668.2</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>3232.56</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>3279.5</v>
+        <v>3282.78</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>43.8</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>42.79</v>
+        <v>42.83</v>
       </c>
       <c r="G464" s="14" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>125.09</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>142.18</v>
+        <v>142.08</v>
       </c>
       <c r="G465" s="14" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>347.07</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>357.34</v>
+        <v>357.69</v>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>4495.02</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>4411.58</v>
+        <v>4415.23</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>535.74</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>495.48</v>
+        <v>495.82</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>537.3</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>526.65</v>
+        <v>526.45</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>1427.79</v>
       </c>
       <c r="F471" s="11" t="n">
-        <v>1233.08</v>
+        <v>1232.94</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>903.58</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>965.4400000000001</v>
+        <v>969.98</v>
       </c>
       <c r="G472" s="12" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>67.55</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>73.43000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="G473" s="12" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>1042.85</v>
       </c>
       <c r="F474" s="11" t="n">
-        <v>967.25</v>
+        <v>969.12</v>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>375.37</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>387.92</v>
+        <v>387.99</v>
       </c>
       <c r="G475" s="14" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>603.63</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>556.64</v>
+        <v>556.67</v>
       </c>
       <c r="G476" s="14" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>216.47</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>221.12</v>
+        <v>221.38</v>
       </c>
       <c r="G477" s="14" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>33.5</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>34.82</v>
+        <v>34.79</v>
       </c>
       <c r="G478" s="14" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>412.96</v>
       </c>
       <c r="F479" s="11" t="n">
-        <v>432.89</v>
+        <v>433.14</v>
       </c>
       <c r="G479" s="14" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>332.08</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>336.28</v>
+        <v>336.19</v>
       </c>
       <c r="G480" s="14" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>4102.09</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>4396.41</v>
+        <v>4392.16</v>
       </c>
       <c r="G481" s="14" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>518.53</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>465.71</v>
+        <v>465.7</v>
       </c>
       <c r="G482" s="14" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>83.01000000000001</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>81.34999999999999</v>
+        <v>81.36</v>
       </c>
       <c r="G483" s="14" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>939.5599999999999</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>969.92</v>
+        <v>969.27</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>1096.05</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>1006.83</v>
+        <v>1006.39</v>
       </c>
       <c r="G485" s="14" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>63.84</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>64.72</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="G486" s="14" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>33941.73</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>33069.75</v>
+        <v>33058.7</v>
       </c>
       <c r="G487" s="14" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>198.1</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>240.08</v>
+        <v>241.83</v>
       </c>
       <c r="G488" s="14" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>2225.58</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>2304.83</v>
+        <v>2304.38</v>
       </c>
       <c r="G491" s="14" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>1354.99</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>1418.13</v>
+        <v>1423.71</v>
       </c>
       <c r="G492" s="14" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>615.25</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>655.3099999999999</v>
+        <v>655.5</v>
       </c>
       <c r="G493" s="14" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>5013.68</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>5242.53</v>
+        <v>5247.36</v>
       </c>
       <c r="G494" s="14" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>825.17</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>858.3200000000001</v>
+        <v>859.08</v>
       </c>
       <c r="G495" s="14" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>924.33</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>892.9299999999999</v>
+        <v>893.23</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>279.02</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>290.37</v>
+        <v>290.39</v>
       </c>
       <c r="G497" s="14" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>305.18</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>324.58</v>
+        <v>324.87</v>
       </c>
       <c r="G498" s="14" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>1490.79</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>1595.81</v>
+        <v>1595.9</v>
       </c>
       <c r="G499" s="14" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>3094.61</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>3065.45</v>
+        <v>3063.73</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 01-Oct-2026  17:17:59    |    Closing Price Date: 01-Oct-2026</t>
+          <t>Scan Run: 02-Oct-2026  16:31:32    |    Closing Price Date: 01-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -596,14 +596,14 @@
         <v>15.4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-Oct-2026  17:17:59</t>
+          <t>02-Oct-2026  16:31:32</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 32.4% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 32.6% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 162 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 163 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         <v>1912.51</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1728.2</v>
+        <v>1727.65</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>730.2</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>795.21</v>
+        <v>795.59</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>1078.7</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1203.68</v>
+        <v>1204.99</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>566.25</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>496.09</v>
+        <v>496.88</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>1373.17</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.66</v>
+        <v>1360.73</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>361.18</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>295.79</v>
+        <v>296.08</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>3148.7</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3220.31</v>
+        <v>3222.92</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>1267.53</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1336.7</v>
+        <v>1337.37</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>426.94</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>396.74</v>
+        <v>396.79</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>1544.15</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1204.76</v>
+        <v>1205.21</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>2607.28</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2856.64</v>
+        <v>2855.45</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>270.87</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>294.69</v>
+        <v>295.05</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>4102.43</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3778.49</v>
+        <v>3781.73</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>2211.79</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2431.06</v>
+        <v>2433.18</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>7565.9</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7287.2</v>
+        <v>7285.09</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>1852.03</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1882.91</v>
+        <v>1884.19</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>1028.73</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>991.45</v>
+        <v>991.91</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>172.27</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>193.69</v>
+        <v>193.86</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>316.78</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>289.38</v>
+        <v>289.54</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>1773.21</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>1618.51</v>
+        <v>1619.23</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>417.57</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>414.47</v>
+        <v>414.44</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>2231.55</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>2265.24</v>
+        <v>2265.47</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>569.78</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>742.86</v>
+        <v>742.4299999999999</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>1744.7</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1654.13</v>
+        <v>1654.28</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>12798.16</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>13499.24</v>
+        <v>13505.47</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>1247.91</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>1263.74</v>
+        <v>1263.42</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>3922.91</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3916.69</v>
+        <v>3917.3</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>3569.3</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>3923.13</v>
+        <v>3925.25</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>5325.33</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5189.38</v>
+        <v>5189.71</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>1009.74</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>1002.14</v>
+        <v>1002.33</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>1554.52</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1506.26</v>
+        <v>1507.34</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>5396</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>5358.9</v>
+        <v>5359.95</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>2538.85</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>2550.14</v>
+        <v>2550.32</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>400.89</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>411.06</v>
+        <v>410.55</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>779.96</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>651.1</v>
+        <v>651.0599999999999</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>393.38</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>454.64</v>
+        <v>455.15</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>3356.51</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3316.81</v>
+        <v>3316.95</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         <v>13431.65</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>13569.13</v>
+        <v>13569.12</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>13066</v>
+        <v>13052.12</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>1406.46</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1365.63</v>
+        <v>1366.41</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>1030.44</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>974.65</v>
+        <v>974.62</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>395.51</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>351.3</v>
+        <v>351.26</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>1992.69</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2142.36</v>
+        <v>2142.99</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>269.94</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>299.05</v>
+        <v>299.12</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>8812.870000000001</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>7460.3</v>
+        <v>7461.16</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>1263</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1309.53</v>
+        <v>1310.51</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>1152.23</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1093.6</v>
+        <v>1093.04</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>406.67</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>402.02</v>
+        <v>401.81</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>169.07</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>164</v>
+        <v>163.98</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>324.44</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>314.27</v>
+        <v>315.1</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>4364.62</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>4081.14</v>
+        <v>4079.35</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>1878.41</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>1821.18</v>
+        <v>1821.5</v>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>296.5</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>292.27</v>
+        <v>291.89</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>204.15</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>186.3</v>
+        <v>186.38</v>
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>1857.88</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>1455.91</v>
+        <v>1455.92</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>994.12</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>957.48</v>
+        <v>957.61</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>3860.49</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>4023.4</v>
+        <v>4024.46</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>218.67</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>164.1</v>
+        <v>164.24</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>2969.73</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>2732.43</v>
+        <v>2733.31</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>4883.86</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4481.37</v>
+        <v>4483.22</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>234.05</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>250.39</v>
+        <v>250.49</v>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>4846.5</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4450.44</v>
+        <v>4455.55</v>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>1361.53</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>1117.08</v>
+        <v>1116.4</v>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>17665.78</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>18443.07</v>
+        <v>18449.93</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
         <v>3258.24</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>3145.55</v>
+        <v>3145.56</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>2754.87</v>
+        <v>2758.48</v>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>1609.81</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1340.74</v>
+        <v>1340.59</v>
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>207.06</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>191.89</v>
+        <v>191.97</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>32112.04</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>29435.38</v>
+        <v>29448.62</v>
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>885.46</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>827.13</v>
+        <v>826.89</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>11236.37</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>11447.15</v>
+        <v>11453.26</v>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>333.21</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>345.45</v>
+        <v>345.49</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>1084.96</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>1111.83</v>
+        <v>1113.14</v>
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>11295.95</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>10348.35</v>
+        <v>10348.86</v>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>360.54</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>386.5</v>
+        <v>386.47</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>1401.98</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1377.28</v>
+        <v>1378.43</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>8645.15</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>8432.09</v>
+        <v>8436.040000000001</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>331.12</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>314</v>
+        <v>314.14</v>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>433.83</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>458.9</v>
+        <v>458.8</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>1461.21</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>1096.34</v>
+        <v>1097.19</v>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>4380.32</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>3753.17</v>
+        <v>3753.46</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>419.37</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>409.34</v>
+        <v>409.63</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>87.3</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>94.29000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>2901.89</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>3104.59</v>
+        <v>3104.92</v>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>14.01</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>12.41</v>
+        <v>12.42</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>150.51</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>143.77</v>
+        <v>143.83</v>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>5022.56</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>5013.51</v>
+        <v>5014.85</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>328.46</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>292.85</v>
+        <v>293.08</v>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>1760.26</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1833.78</v>
+        <v>1833.77</v>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>236.78</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>247.1</v>
+        <v>247.02</v>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>4751.56</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>4548.22</v>
+        <v>4544.44</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>4783.38</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>4154.45</v>
+        <v>4157.09</v>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>2348.44</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>2483.16</v>
+        <v>2479.57</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>2172.72</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>2207.39</v>
+        <v>2207.57</v>
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>186.73</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>187.13</v>
+        <v>187.19</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>682.2</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>611.47</v>
+        <v>611.98</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>274.34</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>382.43</v>
+        <v>382.28</v>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>2885.59</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>2512.01</v>
+        <v>2512.57</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>11270.25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>9913.51</v>
+        <v>9914.309999999999</v>
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44.04</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>43.56</v>
+        <v>43.6</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>7210.91</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>6689.23</v>
+        <v>6687.75</v>
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>2827.37</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>3164.2</v>
+        <v>3166.92</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>544.13</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>606.9400000000001</v>
+        <v>607.15</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>394.67</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>432.56</v>
+        <v>432.77</v>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>2326.66</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2373.95</v>
+        <v>2376.66</v>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>78.44</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>70.23999999999999</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>360.06</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>374.63</v>
+        <v>374.7</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>417.62</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>363.9</v>
+        <v>363.98</v>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>8732.059999999999</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8235.85</v>
+        <v>8237.309999999999</v>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>163.4</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>161.23</v>
+        <v>161.31</v>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>378.73</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>389.44</v>
+        <v>389.46</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>604.25</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>549.62</v>
+        <v>549.74</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>1635.33</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1483.77</v>
+        <v>1484.93</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>240.39</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>254.12</v>
+        <v>254.17</v>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>1447.93</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1330.56</v>
+        <v>1330.5</v>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>269.72</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>279.4</v>
+        <v>279.57</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>968.58</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>977.03</v>
+        <v>976.9299999999999</v>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>4474.12</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>3946.85</v>
+        <v>3941.01</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>2685.72</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>2801.4</v>
+        <v>2801.38</v>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>336.95</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>305.78</v>
+        <v>305.83</v>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>353.73</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>333.66</v>
+        <v>333.56</v>
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>364.87</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>349.73</v>
+        <v>349.66</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>3275.39</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>3203.22</v>
+        <v>3207.12</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>4284.8</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>4517.59</v>
+        <v>4521.58</v>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>1771.11</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>1704.6</v>
+        <v>1705.02</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>404.95</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>336.86</v>
+        <v>336.82</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>398.9</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>396.26</v>
+        <v>396.35</v>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>310.11</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>315.35</v>
+        <v>315.36</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>1427.74</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1387.38</v>
+        <v>1387.85</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>149.5</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>138.76</v>
+        <v>138.9</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>1157.77</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1256.93</v>
+        <v>1256.77</v>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>312.75</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>366.1</v>
+        <v>366.13</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>264.66</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>273.1</v>
+        <v>273.19</v>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>177.66</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>166.68</v>
+        <v>166.58</v>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>754.67</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>706.0700000000001</v>
+        <v>706.15</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>16815.12</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>13564.3</v>
+        <v>13572.62</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>133.42</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>129.96</v>
+        <v>130.09</v>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>2792.39</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>2320.69</v>
+        <v>2321.31</v>
       </c>
       <c r="G142" s="11" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>368</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>428.27</v>
+        <v>428.54</v>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>1027.54</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1087.56</v>
+        <v>1088.32</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>600.65</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>566.38</v>
+        <v>567.45</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>1026.96</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1053.08</v>
+        <v>1054.74</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>1573.32</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>1524.47</v>
+        <v>1524.55</v>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>5337.58</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>5393.78</v>
+        <v>5395.53</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>577.46</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>558.29</v>
+        <v>558.67</v>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>823.42</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>799.5700000000001</v>
+        <v>799.63</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>722.48</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>705.72</v>
+        <v>706.4400000000001</v>
       </c>
       <c r="G152" s="11" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>4941.81</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>4839.14</v>
+        <v>4837.77</v>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>1529.92</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1528.37</v>
+        <v>1529.19</v>
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>1319.84</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>1249.35</v>
+        <v>1249.1</v>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>19626.07</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>17410.13</v>
+        <v>17406.14</v>
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>178.24</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>177.74</v>
+        <v>177.82</v>
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>18.97</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>20.36</v>
+        <v>20.38</v>
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>338.5</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>308.68</v>
+        <v>308.84</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>5135.64</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>4964.48</v>
+        <v>4964.76</v>
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>177.51</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>168.74</v>
+        <v>168.63</v>
       </c>
       <c r="G162" s="11" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>577.62</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>561</v>
+        <v>560.97</v>
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
@@ -7891,10 +7891,10 @@
         <v>10801.49</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>10574.11</v>
+        <v>10574.12</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>9004.01</v>
+        <v>9013.08</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>1195.36</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>1233.84</v>
+        <v>1234.01</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>657.1</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>650.51</v>
+        <v>650.7</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>322.17</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>339.73</v>
+        <v>339.72</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>561.29</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>529.16</v>
+        <v>529.25</v>
       </c>
       <c r="G168" s="11" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>841.11</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>865.88</v>
+        <v>865.83</v>
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>2116.83</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>2074.37</v>
+        <v>2076.55</v>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>1107.6</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>1107.34</v>
+        <v>1109.06</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>1884.54</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1897.86</v>
+        <v>1897.96</v>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
@@ -8287,10 +8287,10 @@
         <v>36480.19</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>36920.89</v>
+        <v>36920.9</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>37672.41</v>
+        <v>37754.57</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>5127.07</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>5378.67</v>
+        <v>5382.27</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>75.86</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>93.91</v>
+        <v>93.97</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>83.84</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>96.98999999999999</v>
+        <v>97.03</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>3497.3</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>3154.88</v>
+        <v>3155.72</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>159.66</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>140.1</v>
+        <v>140.15</v>
       </c>
       <c r="G178" s="11" t="inlineStr">
         <is>
@@ -8541,17 +8541,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>237.65</v>
+        <v>239.28</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>315.87</v>
+        <v>308.58</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>448.71</v>
+        <v>440.49</v>
       </c>
       <c r="F179" s="10" t="n">
         <v/>
@@ -8598,7 +8598,7 @@
         <v>3485.97</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>4134.6</v>
+        <v>4134.62</v>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>2521.17</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>2090.16</v>
+        <v>2090.14</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>1514.36</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>1584.9</v>
+        <v>1585.28</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>7210.45</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>7331.43</v>
+        <v>7335.73</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>1044.25</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>995.99</v>
+        <v>996.25</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>1893.5</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>2020.34</v>
+        <v>2020.14</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>222.35</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>204.76</v>
+        <v>204.92</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>445.05</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>447.7</v>
+        <v>448.15</v>
       </c>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>524.16</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>560.3099999999999</v>
+        <v>560.64</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>22.56</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>22.12</v>
+        <v>22.13</v>
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>1252.34</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>1195.71</v>
+        <v>1195.88</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>966.83</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>928.05</v>
+        <v>927.96</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>1397.85</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>1400.99</v>
+        <v>1401.3</v>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>8230.120000000001</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>7185.99</v>
+        <v>7189.72</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>2032.89</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>2223.25</v>
+        <v>2225.38</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>3264.73</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2772.41</v>
+        <v>2772.13</v>
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>16.48</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>17.23</v>
+        <v>17.26</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>1608.89</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>1655.17</v>
+        <v>1653.98</v>
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>905.02</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>944.38</v>
+        <v>944.3</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>1276.6</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>1231.53</v>
+        <v>1232.24</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>1645.98</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>1463.86</v>
+        <v>1464.51</v>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>1883.89</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>1675.59</v>
+        <v>1676.2</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>114.21</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>111.48</v>
+        <v>111.51</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>45971.44</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>40584.95</v>
+        <v>40595.35</v>
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>508.54</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>489.25</v>
+        <v>489.33</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>805.38</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>879.6</v>
+        <v>879.9299999999999</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>401.2</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>448.06</v>
+        <v>448.27</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>1843.12</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>1897.83</v>
+        <v>1898.02</v>
       </c>
       <c r="G208" s="11" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>1424.13</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>1519.94</v>
+        <v>1518.67</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>82.65000000000001</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>82.29000000000001</v>
+        <v>82.27</v>
       </c>
       <c r="G210" s="11" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>1338.64</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1357.69</v>
+        <v>1357.52</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>21764.93</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>18254.72</v>
+        <v>18245.45</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>2458.95</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>2574.37</v>
+        <v>2567.12</v>
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>1265.57</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>1071.76</v>
+        <v>1073.95</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>457.53</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>532.42</v>
+        <v>533.12</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>369.82</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>383.44</v>
+        <v>383.63</v>
       </c>
       <c r="G216" s="11" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>505.75</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>573.23</v>
+        <v>574.5599999999999</v>
       </c>
       <c r="G217" s="11" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>2366.94</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>2216.49</v>
+        <v>2217.87</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>284.36</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>294.71</v>
+        <v>295.49</v>
       </c>
       <c r="G219" s="11" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>172.51</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>169.06</v>
+        <v>169</v>
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>136.84</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>141.94</v>
+        <v>141.91</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>52.63</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>61.22</v>
+        <v>61.25</v>
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>1845.16</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>1679.64</v>
+        <v>1679.47</v>
       </c>
       <c r="G223" s="11" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>778.26</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>743.9299999999999</v>
+        <v>744.97</v>
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>549.03</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>565.12</v>
+        <v>565.05</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>99.23</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>99.26000000000001</v>
+        <v>99.28</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>2567.11</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>2684.45</v>
+        <v>2685.53</v>
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>1120.71</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>1030.52</v>
+        <v>1031.21</v>
       </c>
       <c r="G228" s="11" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>3192.33</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>3032.8</v>
+        <v>3034.86</v>
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>1401.6</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1372.7</v>
+        <v>1374.37</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>1921.83</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>1831.68</v>
+        <v>1832.4</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>2101.49</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>1963.49</v>
+        <v>1963.6</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>1141.42</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>1054.87</v>
+        <v>1055.28</v>
       </c>
       <c r="G234" s="11" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>301.5</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>288.62</v>
+        <v>288.68</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>1441.07</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>1479.7</v>
+        <v>1479.88</v>
       </c>
       <c r="G236" s="11" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>750.49</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>676.7</v>
+        <v>677.01</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>38.59</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>38.64</v>
+        <v>38.63</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>538.37</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>534.36</v>
+        <v>534.64</v>
       </c>
       <c r="G240" s="11" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>2044.2</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>1777.19</v>
+        <v>1776.7</v>
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>289.68</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>328.14</v>
+        <v>328.97</v>
       </c>
       <c r="G243" s="11" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>980.95</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>905.3200000000001</v>
+        <v>905.67</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>3848.92</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>3594.76</v>
+        <v>3594.32</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>1188.82</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>1289.63</v>
+        <v>1289.83</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>2410.97</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>2362.09</v>
+        <v>2362.15</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>1206.67</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>1173.29</v>
+        <v>1174.13</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>2472.35</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>2555.24</v>
+        <v>2555.82</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>139.48</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>139.6</v>
+        <v>139.63</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>328.62</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>299.56</v>
+        <v>299.54</v>
       </c>
       <c r="G251" s="11" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>469.26</v>
       </c>
       <c r="F252" s="10" t="n">
-        <v>456.22</v>
+        <v>456.03</v>
       </c>
       <c r="G252" s="11" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>274.74</v>
       </c>
       <c r="F253" s="10" t="n">
-        <v>280.63</v>
+        <v>280.64</v>
       </c>
       <c r="G253" s="11" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>1127.78</v>
       </c>
       <c r="F255" s="10" t="n">
-        <v>1114.46</v>
+        <v>1114.29</v>
       </c>
       <c r="G255" s="11" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>1649.24</v>
       </c>
       <c r="F256" s="10" t="n">
-        <v>1672.54</v>
+        <v>1674.04</v>
       </c>
       <c r="G256" s="11" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>631.52</v>
       </c>
       <c r="F257" s="10" t="n">
-        <v>688.27</v>
+        <v>687.77</v>
       </c>
       <c r="G257" s="11" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>1572.92</v>
       </c>
       <c r="F258" s="10" t="n">
-        <v>1727.76</v>
+        <v>1728.73</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>1296.92</v>
       </c>
       <c r="F259" s="10" t="n">
-        <v>1371.74</v>
+        <v>1372.18</v>
       </c>
       <c r="G259" s="11" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1225.75</v>
       </c>
       <c r="F260" s="10" t="n">
-        <v>1332.78</v>
+        <v>1331.29</v>
       </c>
       <c r="G260" s="11" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>407.97</v>
       </c>
       <c r="F261" s="10" t="n">
-        <v>412.86</v>
+        <v>412.97</v>
       </c>
       <c r="G261" s="11" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>1151.69</v>
       </c>
       <c r="F262" s="10" t="n">
-        <v>1054.44</v>
+        <v>1054.85</v>
       </c>
       <c r="G262" s="11" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>567.4</v>
       </c>
       <c r="F263" s="10" t="n">
-        <v>549.02</v>
+        <v>549.58</v>
       </c>
       <c r="G263" s="11" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>2008.43</v>
       </c>
       <c r="F264" s="10" t="n">
-        <v>1862.87</v>
+        <v>1862.05</v>
       </c>
       <c r="G264" s="11" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>846.34</v>
       </c>
       <c r="F265" s="10" t="n">
-        <v>830.74</v>
+        <v>830.63</v>
       </c>
       <c r="G265" s="11" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>215.16</v>
       </c>
       <c r="F266" s="10" t="n">
-        <v>258.88</v>
+        <v>258.94</v>
       </c>
       <c r="G266" s="11" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>117.56</v>
       </c>
       <c r="F267" s="10" t="n">
-        <v>126.55</v>
+        <v>126.6</v>
       </c>
       <c r="G267" s="11" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>850.74</v>
       </c>
       <c r="F268" s="10" t="n">
-        <v>744.78</v>
+        <v>744.97</v>
       </c>
       <c r="G268" s="11" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>7336.69</v>
       </c>
       <c r="F269" s="10" t="n">
-        <v>7861.59</v>
+        <v>7867.94</v>
       </c>
       <c r="G269" s="11" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>219.09</v>
       </c>
       <c r="F270" s="10" t="n">
-        <v>216.33</v>
+        <v>216.43</v>
       </c>
       <c r="G270" s="11" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>84.15000000000001</v>
       </c>
       <c r="F271" s="10" t="n">
-        <v>89.26000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="G271" s="11" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>82.01000000000001</v>
       </c>
       <c r="F272" s="10" t="n">
-        <v>75.38</v>
+        <v>75.37</v>
       </c>
       <c r="G272" s="11" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>485.62</v>
       </c>
       <c r="F273" s="10" t="n">
-        <v>532.62</v>
+        <v>532.63</v>
       </c>
       <c r="G273" s="11" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>481.79</v>
       </c>
       <c r="F274" s="10" t="n">
-        <v>478.59</v>
+        <v>478.2</v>
       </c>
       <c r="G274" s="11" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>529.34</v>
       </c>
       <c r="F275" s="10" t="n">
-        <v>530.75</v>
+        <v>530.86</v>
       </c>
       <c r="G275" s="11" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>487.51</v>
       </c>
       <c r="F276" s="10" t="n">
-        <v>497.03</v>
+        <v>497.38</v>
       </c>
       <c r="G276" s="11" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>2161.26</v>
       </c>
       <c r="F277" s="10" t="n">
-        <v>1813.54</v>
+        <v>1813.69</v>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>249.25</v>
       </c>
       <c r="F278" s="10" t="n">
-        <v>216.99</v>
+        <v>216.9</v>
       </c>
       <c r="G278" s="11" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>106.26</v>
       </c>
       <c r="F279" s="10" t="n">
-        <v>116.31</v>
+        <v>116.33</v>
       </c>
       <c r="G279" s="11" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>35400.09</v>
       </c>
       <c r="F280" s="10" t="n">
-        <v>35057.67</v>
+        <v>35071.7</v>
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>919.45</v>
       </c>
       <c r="F281" s="10" t="n">
-        <v>1024.11</v>
+        <v>1024.57</v>
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>2744.72</v>
       </c>
       <c r="F282" s="10" t="n">
-        <v>2660.42</v>
+        <v>2670.48</v>
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>84.42</v>
       </c>
       <c r="F283" s="10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>234.71</v>
       </c>
       <c r="F284" s="10" t="n">
-        <v>256.81</v>
+        <v>257.08</v>
       </c>
       <c r="G284" s="11" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>692.91</v>
       </c>
       <c r="F285" s="10" t="n">
-        <v>621.16</v>
+        <v>622.6</v>
       </c>
       <c r="G285" s="11" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>768.11</v>
       </c>
       <c r="F286" s="10" t="n">
-        <v>728.51</v>
+        <v>729.21</v>
       </c>
       <c r="G286" s="11" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>1730.06</v>
       </c>
       <c r="F287" s="10" t="n">
-        <v>1664.7</v>
+        <v>1663.03</v>
       </c>
       <c r="G287" s="11" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>1306.15</v>
       </c>
       <c r="F288" s="10" t="n">
-        <v>1035.39</v>
+        <v>1035.83</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>885.5</v>
       </c>
       <c r="F289" s="10" t="n">
-        <v>943.0599999999999</v>
+        <v>943.97</v>
       </c>
       <c r="G289" s="11" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>235.75</v>
       </c>
       <c r="F290" s="10" t="n">
-        <v>210.47</v>
+        <v>210.71</v>
       </c>
       <c r="G290" s="11" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>526.13</v>
       </c>
       <c r="F291" s="10" t="n">
-        <v>516.83</v>
+        <v>516.6799999999999</v>
       </c>
       <c r="G291" s="11" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>1505.7</v>
       </c>
       <c r="F292" s="10" t="n">
-        <v>1618.5</v>
+        <v>1617.87</v>
       </c>
       <c r="G292" s="11" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>3812.93</v>
       </c>
       <c r="F293" s="10" t="n">
-        <v>3862.97</v>
+        <v>3862.37</v>
       </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>284.97</v>
       </c>
       <c r="F294" s="10" t="n">
-        <v>279.99</v>
+        <v>279.88</v>
       </c>
       <c r="G294" s="11" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>86.64</v>
       </c>
       <c r="F295" s="10" t="n">
-        <v>95.37</v>
+        <v>95.53</v>
       </c>
       <c r="G295" s="11" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>128521.35</v>
       </c>
       <c r="F296" s="10" t="n">
-        <v>133588.02</v>
+        <v>133696.56</v>
       </c>
       <c r="G296" s="11" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>526.63</v>
       </c>
       <c r="F297" s="10" t="n">
-        <v>519.0700000000001</v>
+        <v>519.3200000000001</v>
       </c>
       <c r="G297" s="11" t="inlineStr">
         <is>
@@ -13787,10 +13787,10 @@
         <v>1559.66</v>
       </c>
       <c r="E298" s="10" t="n">
-        <v>1574.14</v>
+        <v>1574.15</v>
       </c>
       <c r="F298" s="10" t="n">
-        <v>1587.03</v>
+        <v>1588.13</v>
       </c>
       <c r="G298" s="11" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>76.23</v>
       </c>
       <c r="F299" s="10" t="n">
-        <v>77.76000000000001</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="G299" s="11" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>472.85</v>
       </c>
       <c r="F300" s="10" t="n">
-        <v>490.76</v>
+        <v>491.47</v>
       </c>
       <c r="G300" s="11" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>732.39</v>
       </c>
       <c r="F301" s="10" t="n">
-        <v>747.9299999999999</v>
+        <v>747.91</v>
       </c>
       <c r="G301" s="11" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>1242.36</v>
       </c>
       <c r="F303" s="10" t="n">
-        <v>1134.75</v>
+        <v>1135.3</v>
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>554.21</v>
       </c>
       <c r="F304" s="10" t="n">
-        <v>564.33</v>
+        <v>564.58</v>
       </c>
       <c r="G304" s="11" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>1046.43</v>
       </c>
       <c r="F305" s="10" t="n">
-        <v>955.21</v>
+        <v>955.64</v>
       </c>
       <c r="G305" s="11" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>149.58</v>
       </c>
       <c r="F306" s="10" t="n">
-        <v>152.67</v>
+        <v>153.43</v>
       </c>
       <c r="G306" s="11" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>616.67</v>
       </c>
       <c r="F307" s="10" t="n">
-        <v>628.1799999999999</v>
+        <v>627.97</v>
       </c>
       <c r="G307" s="11" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>961.0700000000001</v>
       </c>
       <c r="F309" s="10" t="n">
-        <v>873.13</v>
+        <v>873.86</v>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>569.9400000000001</v>
       </c>
       <c r="F310" s="10" t="n">
-        <v>616.98</v>
+        <v>617.23</v>
       </c>
       <c r="G310" s="11" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>394.51</v>
       </c>
       <c r="F311" s="10" t="n">
-        <v>367.2</v>
+        <v>367.25</v>
       </c>
       <c r="G311" s="11" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>3479.7</v>
       </c>
       <c r="F312" s="10" t="n">
-        <v>3600.83</v>
+        <v>3598.38</v>
       </c>
       <c r="G312" s="11" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>1353.4</v>
       </c>
       <c r="F313" s="10" t="n">
-        <v>1189.37</v>
+        <v>1190.75</v>
       </c>
       <c r="G313" s="11" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>10981.3</v>
       </c>
       <c r="F314" s="10" t="n">
-        <v>10937.27</v>
+        <v>10935.17</v>
       </c>
       <c r="G314" s="11" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>1414.33</v>
       </c>
       <c r="F315" s="10" t="n">
-        <v>1333.72</v>
+        <v>1334.24</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>1012.16</v>
       </c>
       <c r="F316" s="10" t="n">
-        <v>988.02</v>
+        <v>987.54</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>1197.43</v>
       </c>
       <c r="F317" s="10" t="n">
-        <v>1088.96</v>
+        <v>1089.06</v>
       </c>
       <c r="G317" s="11" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>1486.18</v>
       </c>
       <c r="F318" s="10" t="n">
-        <v>1217.38</v>
+        <v>1217.88</v>
       </c>
       <c r="G318" s="11" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>1846.13</v>
       </c>
       <c r="F319" s="10" t="n">
-        <v>1788.37</v>
+        <v>1788.4</v>
       </c>
       <c r="G319" s="11" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>677.7</v>
       </c>
       <c r="F320" s="10" t="n">
-        <v>758.1</v>
+        <v>759.72</v>
       </c>
       <c r="G320" s="11" t="inlineStr">
         <is>
@@ -14799,10 +14799,10 @@
         <v>3350.19</v>
       </c>
       <c r="E321" s="10" t="n">
-        <v>3416.05</v>
+        <v>3416.06</v>
       </c>
       <c r="F321" s="10" t="n">
-        <v>3488.7</v>
+        <v>3492.23</v>
       </c>
       <c r="G321" s="11" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>2330.39</v>
       </c>
       <c r="F322" s="10" t="n">
-        <v>1600.31</v>
+        <v>1601.28</v>
       </c>
       <c r="G322" s="11" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>459.27</v>
       </c>
       <c r="F323" s="10" t="n">
-        <v>449.21</v>
+        <v>448.99</v>
       </c>
       <c r="G323" s="11" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>1542.98</v>
       </c>
       <c r="F324" s="10" t="n">
-        <v>1648.56</v>
+        <v>1649.14</v>
       </c>
       <c r="G324" s="11" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>114.73</v>
       </c>
       <c r="F325" s="10" t="n">
-        <v>124.7</v>
+        <v>124.92</v>
       </c>
       <c r="G325" s="11" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>4476.56</v>
       </c>
       <c r="F326" s="10" t="n">
-        <v>3995.07</v>
+        <v>3995.72</v>
       </c>
       <c r="G326" s="11" t="inlineStr">
         <is>
@@ -15063,10 +15063,10 @@
         <v>609.12</v>
       </c>
       <c r="E327" s="10" t="n">
-        <v>629.9299999999999</v>
+        <v>629.9400000000001</v>
       </c>
       <c r="F327" s="10" t="n">
-        <v>633.03</v>
+        <v>633.12</v>
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>423.87</v>
       </c>
       <c r="F328" s="10" t="n">
-        <v>532.8099999999999</v>
+        <v>534.37</v>
       </c>
       <c r="G328" s="11" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>161.56</v>
       </c>
       <c r="F329" s="10" t="n">
-        <v>171.84</v>
+        <v>171.96</v>
       </c>
       <c r="G329" s="11" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>572.26</v>
       </c>
       <c r="F330" s="10" t="n">
-        <v>612.65</v>
+        <v>613.29</v>
       </c>
       <c r="G330" s="11" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>2456.23</v>
       </c>
       <c r="F331" s="10" t="n">
-        <v>2843.37</v>
+        <v>2843.08</v>
       </c>
       <c r="G331" s="11" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>1726.26</v>
       </c>
       <c r="F332" s="10" t="n">
-        <v>1942.58</v>
+        <v>1949.15</v>
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>261.84</v>
       </c>
       <c r="F333" s="10" t="n">
-        <v>297.01</v>
+        <v>296.97</v>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>1418.5</v>
       </c>
       <c r="F334" s="10" t="n">
-        <v>1297.95</v>
+        <v>1297.9</v>
       </c>
       <c r="G334" s="11" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>1759.9</v>
       </c>
       <c r="F335" s="10" t="n">
-        <v>1864.51</v>
+        <v>1865.29</v>
       </c>
       <c r="G335" s="11" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>6313.05</v>
       </c>
       <c r="F336" s="10" t="n">
-        <v>6430.09</v>
+        <v>6445.69</v>
       </c>
       <c r="G336" s="11" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>107.76</v>
       </c>
       <c r="F337" s="10" t="n">
-        <v>118.63</v>
+        <v>118.7</v>
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>1734.14</v>
       </c>
       <c r="F338" s="10" t="n">
-        <v>1725.91</v>
+        <v>1726.98</v>
       </c>
       <c r="G338" s="11" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>1318.29</v>
       </c>
       <c r="F339" s="10" t="n">
-        <v>1398.87</v>
+        <v>1399.85</v>
       </c>
       <c r="G339" s="11" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>894.67</v>
       </c>
       <c r="F340" s="10" t="n">
-        <v>910.4299999999999</v>
+        <v>911.01</v>
       </c>
       <c r="G340" s="11" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>1809.08</v>
       </c>
       <c r="F341" s="10" t="n">
-        <v>1743.83</v>
+        <v>1743.87</v>
       </c>
       <c r="G341" s="11" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>737.0599999999999</v>
       </c>
       <c r="F342" s="10" t="n">
-        <v>748.39</v>
+        <v>748.35</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>2457.39</v>
       </c>
       <c r="F343" s="10" t="n">
-        <v>2427.07</v>
+        <v>2427.96</v>
       </c>
       <c r="G343" s="11" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>2135.39</v>
       </c>
       <c r="F344" s="10" t="n">
-        <v>1861.96</v>
+        <v>1861.71</v>
       </c>
       <c r="G344" s="11" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>460.21</v>
       </c>
       <c r="F345" s="10" t="n">
-        <v>395.62</v>
+        <v>395.68</v>
       </c>
       <c r="G345" s="11" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>572.88</v>
       </c>
       <c r="F346" s="10" t="n">
-        <v>536.04</v>
+        <v>536.27</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>3379.87</v>
       </c>
       <c r="F347" s="10" t="n">
-        <v>3558.26</v>
+        <v>3559.42</v>
       </c>
       <c r="G347" s="11" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>947.5</v>
       </c>
       <c r="F348" s="10" t="n">
-        <v>1099.87</v>
+        <v>1099.98</v>
       </c>
       <c r="G348" s="11" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>22.14</v>
       </c>
       <c r="F349" s="10" t="n">
-        <v>28.16</v>
+        <v>28.29</v>
       </c>
       <c r="G349" s="11" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>1251.68</v>
       </c>
       <c r="F350" s="10" t="n">
-        <v>1261.64</v>
+        <v>1262.84</v>
       </c>
       <c r="G350" s="11" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>1579.76</v>
       </c>
       <c r="F351" s="10" t="n">
-        <v>1629.81</v>
+        <v>1630.15</v>
       </c>
       <c r="G351" s="11" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>23642.44</v>
       </c>
       <c r="F353" s="10" t="n">
-        <v>25238.01</v>
+        <v>25261.08</v>
       </c>
       <c r="G353" s="11" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>1207.14</v>
       </c>
       <c r="F354" s="10" t="n">
-        <v>1142.51</v>
+        <v>1142.53</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>181.16</v>
       </c>
       <c r="F355" s="10" t="n">
-        <v>195.1</v>
+        <v>195.34</v>
       </c>
       <c r="G355" s="11" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>37</v>
       </c>
       <c r="F356" s="10" t="n">
-        <v>39.42</v>
+        <v>39.44</v>
       </c>
       <c r="G356" s="11" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>242.01</v>
       </c>
       <c r="F358" s="10" t="n">
-        <v>272.03</v>
+        <v>272.15</v>
       </c>
       <c r="G358" s="11" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>425.31</v>
       </c>
       <c r="F359" s="10" t="n">
-        <v>446.92</v>
+        <v>446.82</v>
       </c>
       <c r="G359" s="11" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>478.67</v>
       </c>
       <c r="F361" s="10" t="n">
-        <v>542.36</v>
+        <v>542.59</v>
       </c>
       <c r="G361" s="11" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>283.39</v>
       </c>
       <c r="F362" s="10" t="n">
-        <v>272.63</v>
+        <v>272.71</v>
       </c>
       <c r="G362" s="11" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>689.71</v>
       </c>
       <c r="F363" s="10" t="n">
-        <v>630.24</v>
+        <v>630.28</v>
       </c>
       <c r="G363" s="11" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>1136.86</v>
       </c>
       <c r="F364" s="10" t="n">
-        <v>1030.5</v>
+        <v>1031.01</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>1894.05</v>
       </c>
       <c r="F365" s="10" t="n">
-        <v>1677.7</v>
+        <v>1678.65</v>
       </c>
       <c r="G365" s="11" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>302.83</v>
       </c>
       <c r="F367" s="10" t="n">
-        <v>264.46</v>
+        <v>264.48</v>
       </c>
       <c r="G367" s="11" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>419.59</v>
       </c>
       <c r="F368" s="10" t="n">
-        <v>433.36</v>
+        <v>433.54</v>
       </c>
       <c r="G368" s="11" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>272.04</v>
       </c>
       <c r="F369" s="10" t="n">
-        <v>312.82</v>
+        <v>312.8</v>
       </c>
       <c r="G369" s="11" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>493.33</v>
       </c>
       <c r="F370" s="10" t="n">
-        <v>465.42</v>
+        <v>466.08</v>
       </c>
       <c r="G370" s="11" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>1880.11</v>
       </c>
       <c r="F372" s="10" t="n">
-        <v>1874.75</v>
+        <v>1877.58</v>
       </c>
       <c r="G372" s="11" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>5136.26</v>
       </c>
       <c r="F373" s="10" t="n">
-        <v>5407.76</v>
+        <v>5415.86</v>
       </c>
       <c r="G373" s="11" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>1950.92</v>
       </c>
       <c r="F374" s="10" t="n">
-        <v>1864.51</v>
+        <v>1864.6</v>
       </c>
       <c r="G374" s="11" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>297.75</v>
       </c>
       <c r="F375" s="10" t="n">
-        <v>340.03</v>
+        <v>339.98</v>
       </c>
       <c r="G375" s="11" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>1279.21</v>
       </c>
       <c r="F376" s="10" t="n">
-        <v>1428.57</v>
+        <v>1428.83</v>
       </c>
       <c r="G376" s="11" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>4187.26</v>
       </c>
       <c r="F377" s="10" t="n">
-        <v>4096.96</v>
+        <v>4097.84</v>
       </c>
       <c r="G377" s="11" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>1433.65</v>
       </c>
       <c r="F378" s="10" t="n">
-        <v>1359.54</v>
+        <v>1360.93</v>
       </c>
       <c r="G378" s="11" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>861.15</v>
       </c>
       <c r="F379" s="10" t="n">
-        <v>915.78</v>
+        <v>916.16</v>
       </c>
       <c r="G379" s="11" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>148.15</v>
       </c>
       <c r="F380" s="10" t="n">
-        <v>156.42</v>
+        <v>156.64</v>
       </c>
       <c r="G380" s="11" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>857.75</v>
       </c>
       <c r="F381" s="10" t="n">
-        <v>841.63</v>
+        <v>842.3099999999999</v>
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>1725.27</v>
       </c>
       <c r="F382" s="10" t="n">
-        <v>1590.5</v>
+        <v>1593.34</v>
       </c>
       <c r="G382" s="11" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>1090.72</v>
       </c>
       <c r="F383" s="10" t="n">
-        <v>1068.88</v>
+        <v>1068.73</v>
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
@@ -17571,10 +17571,10 @@
         <v>1163.49</v>
       </c>
       <c r="E384" s="10" t="n">
-        <v>1175.79</v>
+        <v>1175.8</v>
       </c>
       <c r="F384" s="10" t="n">
-        <v>1164.57</v>
+        <v>1166.14</v>
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>240.51</v>
       </c>
       <c r="F385" s="10" t="n">
-        <v>250.69</v>
+        <v>250.84</v>
       </c>
       <c r="G385" s="11" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>1289.9</v>
       </c>
       <c r="F386" s="10" t="n">
-        <v>1433.8</v>
+        <v>1434.15</v>
       </c>
       <c r="G386" s="11" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>2637.39</v>
       </c>
       <c r="F387" s="10" t="n">
-        <v>2287.11</v>
+        <v>2289.22</v>
       </c>
       <c r="G387" s="11" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>733.58</v>
       </c>
       <c r="F388" s="10" t="n">
-        <v>732.74</v>
+        <v>732.58</v>
       </c>
       <c r="G388" s="11" t="inlineStr">
         <is>
@@ -17762,9 +17762,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I388" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I388" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J388" s="13" t="inlineStr">
@@ -17794,7 +17794,7 @@
         <v>470.75</v>
       </c>
       <c r="F389" s="10" t="n">
-        <v>481.51</v>
+        <v>481.81</v>
       </c>
       <c r="G389" s="11" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>640.0700000000001</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>581.8200000000001</v>
+        <v>581.97</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>187.13</v>
       </c>
       <c r="F391" s="10" t="n">
-        <v>200.36</v>
+        <v>200.52</v>
       </c>
       <c r="G391" s="11" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>366.57</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>394.9</v>
+        <v>395.33</v>
       </c>
       <c r="G392" s="11" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>1429.48</v>
       </c>
       <c r="F393" s="10" t="n">
-        <v>1384.92</v>
+        <v>1386.26</v>
       </c>
       <c r="G393" s="11" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>1001.24</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>1074.64</v>
+        <v>1075.42</v>
       </c>
       <c r="G394" s="11" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>331.05</v>
       </c>
       <c r="F395" s="10" t="n">
-        <v>338.17</v>
+        <v>338.28</v>
       </c>
       <c r="G395" s="11" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>4020.84</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>4020.24</v>
+        <v>4020.38</v>
       </c>
       <c r="G396" s="11" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>24.7</v>
       </c>
       <c r="F397" s="10" t="n">
-        <v>26.29</v>
+        <v>26.31</v>
       </c>
       <c r="G397" s="11" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>284.11</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>252.81</v>
+        <v>252.72</v>
       </c>
       <c r="G398" s="11" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>1643.63</v>
       </c>
       <c r="F399" s="10" t="n">
-        <v>1663.68</v>
+        <v>1665.57</v>
       </c>
       <c r="G399" s="11" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>660.3</v>
       </c>
       <c r="F401" s="10" t="n">
-        <v>712.55</v>
+        <v>713.64</v>
       </c>
       <c r="G401" s="11" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>764.78</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>751.3099999999999</v>
+        <v>751.4</v>
       </c>
       <c r="G402" s="11" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>656.95</v>
       </c>
       <c r="F403" s="10" t="n">
-        <v>670.21</v>
+        <v>670.47</v>
       </c>
       <c r="G403" s="11" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>1949.63</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>2043.02</v>
+        <v>2041.64</v>
       </c>
       <c r="G404" s="11" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>1217.74</v>
       </c>
       <c r="F405" s="10" t="n">
-        <v>1240.75</v>
+        <v>1240.2</v>
       </c>
       <c r="G405" s="11" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>575.73</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>576.84</v>
+        <v>577.05</v>
       </c>
       <c r="G406" s="11" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>780.5599999999999</v>
       </c>
       <c r="F407" s="10" t="n">
-        <v>864.3099999999999</v>
+        <v>864.73</v>
       </c>
       <c r="G407" s="11" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>2778.17</v>
       </c>
       <c r="F408" s="10" t="n">
-        <v>2600.31</v>
+        <v>2601.49</v>
       </c>
       <c r="G408" s="11" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>267.66</v>
       </c>
       <c r="F409" s="10" t="n">
-        <v>236.37</v>
+        <v>236.42</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>189.35</v>
       </c>
       <c r="F410" s="10" t="n">
-        <v>183.37</v>
+        <v>183.42</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>274.11</v>
       </c>
       <c r="F411" s="10" t="n">
-        <v>305.81</v>
+        <v>305.92</v>
       </c>
       <c r="G411" s="11" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>1000.28</v>
       </c>
       <c r="F414" s="10" t="n">
-        <v>1090.56</v>
+        <v>1089.53</v>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>481.85</v>
       </c>
       <c r="F415" s="10" t="n">
-        <v>496.59</v>
+        <v>497.19</v>
       </c>
       <c r="G415" s="11" t="inlineStr">
         <is>
@@ -18979,10 +18979,10 @@
         <v>380.59</v>
       </c>
       <c r="E416" s="10" t="n">
-        <v>387.59</v>
+        <v>387.6</v>
       </c>
       <c r="F416" s="10" t="n">
-        <v>430.19</v>
+        <v>430.48</v>
       </c>
       <c r="G416" s="11" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>85.3</v>
       </c>
       <c r="F417" s="10" t="n">
-        <v>100.73</v>
+        <v>100.78</v>
       </c>
       <c r="G417" s="11" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>605.3099999999999</v>
       </c>
       <c r="F418" s="10" t="n">
-        <v>598.97</v>
+        <v>599.4400000000001</v>
       </c>
       <c r="G418" s="11" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>655.75</v>
       </c>
       <c r="F419" s="10" t="n">
-        <v>576.87</v>
+        <v>576.95</v>
       </c>
       <c r="G419" s="11" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>495.48</v>
       </c>
       <c r="F420" s="10" t="n">
-        <v>451.13</v>
+        <v>451.08</v>
       </c>
       <c r="G420" s="11" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>282.98</v>
       </c>
       <c r="F421" s="10" t="n">
-        <v>245.51</v>
+        <v>245.74</v>
       </c>
       <c r="G421" s="11" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>139.94</v>
       </c>
       <c r="F422" s="10" t="n">
-        <v>152.63</v>
+        <v>152.72</v>
       </c>
       <c r="G422" s="11" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>778.28</v>
       </c>
       <c r="F423" s="10" t="n">
-        <v>731.14</v>
+        <v>731.38</v>
       </c>
       <c r="G423" s="11" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>4570.51</v>
       </c>
       <c r="F424" s="10" t="n">
-        <v>4651.27</v>
+        <v>4652.4</v>
       </c>
       <c r="G424" s="11" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>6482.42</v>
       </c>
       <c r="F425" s="10" t="n">
-        <v>6679.39</v>
+        <v>6681.11</v>
       </c>
       <c r="G425" s="11" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>444.03</v>
       </c>
       <c r="F426" s="10" t="n">
-        <v>472.48</v>
+        <v>472.96</v>
       </c>
       <c r="G426" s="11" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>835.0599999999999</v>
       </c>
       <c r="F427" s="10" t="n">
-        <v>824.2</v>
+        <v>824.26</v>
       </c>
       <c r="G427" s="11" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>126.63</v>
       </c>
       <c r="F428" s="10" t="n">
-        <v>131.22</v>
+        <v>131.4</v>
       </c>
       <c r="G428" s="11" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>183.49</v>
       </c>
       <c r="F429" s="10" t="n">
-        <v>172.87</v>
+        <v>173.03</v>
       </c>
       <c r="G429" s="11" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>1795.42</v>
       </c>
       <c r="F430" s="10" t="n">
-        <v>1731.83</v>
+        <v>1731.81</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>4354.3</v>
       </c>
       <c r="F431" s="10" t="n">
-        <v>4639.56</v>
+        <v>4640.05</v>
       </c>
       <c r="G431" s="11" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>380.53</v>
       </c>
       <c r="F433" s="10" t="n">
-        <v>400.85</v>
+        <v>400.81</v>
       </c>
       <c r="G433" s="12" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>1273.76</v>
       </c>
       <c r="F434" s="10" t="n">
-        <v>1364.86</v>
+        <v>1365.68</v>
       </c>
       <c r="G434" s="11" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>500.69</v>
       </c>
       <c r="F435" s="10" t="n">
-        <v>466.89</v>
+        <v>467.06</v>
       </c>
       <c r="G435" s="11" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>148.8</v>
       </c>
       <c r="F436" s="10" t="n">
-        <v>161.41</v>
+        <v>161.52</v>
       </c>
       <c r="G436" s="11" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>1518.92</v>
       </c>
       <c r="F437" s="10" t="n">
-        <v>1571.57</v>
+        <v>1572.12</v>
       </c>
       <c r="G437" s="11" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>2910.39</v>
       </c>
       <c r="F438" s="10" t="n">
-        <v>3080.98</v>
+        <v>3081.18</v>
       </c>
       <c r="G438" s="11" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>742.98</v>
       </c>
       <c r="F439" s="10" t="n">
-        <v>819.21</v>
+        <v>822.67</v>
       </c>
       <c r="G439" s="11" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>657.23</v>
       </c>
       <c r="F440" s="10" t="n">
-        <v>737.96</v>
+        <v>738.47</v>
       </c>
       <c r="G440" s="11" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>809.02</v>
       </c>
       <c r="F441" s="10" t="n">
-        <v>842.72</v>
+        <v>844.8200000000001</v>
       </c>
       <c r="G441" s="11" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>237.72</v>
       </c>
       <c r="F442" s="10" t="n">
-        <v>265.96</v>
+        <v>266.24</v>
       </c>
       <c r="G442" s="11" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>673.11</v>
       </c>
       <c r="F443" s="10" t="n">
-        <v>679.09</v>
+        <v>679.29</v>
       </c>
       <c r="G443" s="11" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>1290.17</v>
       </c>
       <c r="F444" s="10" t="n">
-        <v>1070.14</v>
+        <v>1070.4</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20255,10 +20255,10 @@
         <v>22180.71</v>
       </c>
       <c r="E445" s="10" t="n">
-        <v>21152.99</v>
+        <v>21153</v>
       </c>
       <c r="F445" s="10" t="n">
-        <v>18611.15</v>
+        <v>18617.82</v>
       </c>
       <c r="G445" s="11" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>1150.34</v>
       </c>
       <c r="F446" s="10" t="n">
-        <v>1126.48</v>
+        <v>1126.17</v>
       </c>
       <c r="G446" s="11" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>267.24</v>
       </c>
       <c r="F447" s="10" t="n">
-        <v>316.46</v>
+        <v>316.74</v>
       </c>
       <c r="G447" s="11" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>446.53</v>
       </c>
       <c r="F448" s="10" t="n">
-        <v>484.92</v>
+        <v>484.58</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>1377.36</v>
       </c>
       <c r="F449" s="10" t="n">
-        <v>1289.04</v>
+        <v>1291.05</v>
       </c>
       <c r="G449" s="11" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>507.75</v>
       </c>
       <c r="F450" s="10" t="n">
-        <v>514.3099999999999</v>
+        <v>514.25</v>
       </c>
       <c r="G450" s="11" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>252</v>
       </c>
       <c r="F451" s="10" t="n">
-        <v>264.47</v>
+        <v>264.43</v>
       </c>
       <c r="G451" s="11" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>1300.79</v>
       </c>
       <c r="F452" s="10" t="n">
-        <v>1426.02</v>
+        <v>1423.67</v>
       </c>
       <c r="G452" s="11" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>494.33</v>
       </c>
       <c r="F453" s="10" t="n">
-        <v>521.02</v>
+        <v>520.86</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>92.88</v>
       </c>
       <c r="F454" s="10" t="n">
-        <v>95.42</v>
+        <v>95.38</v>
       </c>
       <c r="G454" s="11" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>197.46</v>
       </c>
       <c r="F455" s="10" t="n">
-        <v>160.64</v>
+        <v>160.99</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>26597.61</v>
       </c>
       <c r="F456" s="10" t="n">
-        <v>26920.99</v>
+        <v>26926.74</v>
       </c>
       <c r="G456" s="12" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>37.37</v>
       </c>
       <c r="F457" s="10" t="n">
-        <v>42.58</v>
+        <v>42.7</v>
       </c>
       <c r="G457" s="11" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>562.53</v>
       </c>
       <c r="F458" s="10" t="n">
-        <v>579.9400000000001</v>
+        <v>580.84</v>
       </c>
       <c r="G458" s="11" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>1782.49</v>
       </c>
       <c r="F459" s="10" t="n">
-        <v>1693.47</v>
+        <v>1693.31</v>
       </c>
       <c r="G459" s="11" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>791.28</v>
       </c>
       <c r="F460" s="10" t="n">
-        <v>826.78</v>
+        <v>826.58</v>
       </c>
       <c r="G460" s="11" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>1699.03</v>
       </c>
       <c r="F461" s="10" t="n">
-        <v>1665.83</v>
+        <v>1668.95</v>
       </c>
       <c r="G461" s="11" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>3209.44</v>
       </c>
       <c r="F463" s="10" t="n">
-        <v>3271.31</v>
+        <v>3271.36</v>
       </c>
       <c r="G463" s="11" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>43.11</v>
       </c>
       <c r="F464" s="10" t="n">
-        <v>42.71</v>
+        <v>42.75</v>
       </c>
       <c r="G464" s="11" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>117.54</v>
       </c>
       <c r="F465" s="10" t="n">
-        <v>136.29</v>
+        <v>136.39</v>
       </c>
       <c r="G465" s="11" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>31.08</v>
       </c>
       <c r="F466" s="10" t="n">
-        <v>33.08</v>
+        <v>33.1</v>
       </c>
       <c r="G466" s="11" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>342.69</v>
       </c>
       <c r="F467" s="10" t="n">
-        <v>354.06</v>
+        <v>354.19</v>
       </c>
       <c r="G467" s="11" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>4513.19</v>
       </c>
       <c r="F468" s="10" t="n">
-        <v>4447.39</v>
+        <v>4452.23</v>
       </c>
       <c r="G468" s="11" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>531.02</v>
       </c>
       <c r="F469" s="10" t="n">
-        <v>500.24</v>
+        <v>500.56</v>
       </c>
       <c r="G469" s="11" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>541.24</v>
       </c>
       <c r="F470" s="10" t="n">
-        <v>530.34</v>
+        <v>530.79</v>
       </c>
       <c r="G470" s="11" t="inlineStr">
         <is>
@@ -21399,10 +21399,10 @@
         <v>1489.04</v>
       </c>
       <c r="E471" s="10" t="n">
-        <v>1455.95</v>
+        <v>1455.96</v>
       </c>
       <c r="F471" s="10" t="n">
-        <v>1265.21</v>
+        <v>1266.28</v>
       </c>
       <c r="G471" s="11" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>901.84</v>
       </c>
       <c r="F472" s="10" t="n">
-        <v>960.74</v>
+        <v>961.13</v>
       </c>
       <c r="G472" s="11" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>65.20999999999999</v>
       </c>
       <c r="F473" s="10" t="n">
-        <v>71.91</v>
+        <v>72</v>
       </c>
       <c r="G473" s="11" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>1034.88</v>
       </c>
       <c r="F474" s="10" t="n">
-        <v>976.02</v>
+        <v>976.47</v>
       </c>
       <c r="G474" s="11" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>353.93</v>
       </c>
       <c r="F475" s="10" t="n">
-        <v>378.74</v>
+        <v>379.66</v>
       </c>
       <c r="G475" s="11" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>604.4299999999999</v>
       </c>
       <c r="F476" s="10" t="n">
-        <v>563.38</v>
+        <v>563.5700000000001</v>
       </c>
       <c r="G476" s="11" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>209.03</v>
       </c>
       <c r="F477" s="10" t="n">
-        <v>215.45</v>
+        <v>215.58</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>32.75</v>
       </c>
       <c r="F478" s="10" t="n">
-        <v>34.3</v>
+        <v>34.32</v>
       </c>
       <c r="G478" s="11" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>399.88</v>
       </c>
       <c r="F479" s="10" t="n">
-        <v>426.11</v>
+        <v>426.23</v>
       </c>
       <c r="G479" s="11" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>331.04</v>
       </c>
       <c r="F480" s="10" t="n">
-        <v>334.77</v>
+        <v>335.1</v>
       </c>
       <c r="G480" s="11" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>3947.39</v>
       </c>
       <c r="F481" s="10" t="n">
-        <v>4312.52</v>
+        <v>4316.26</v>
       </c>
       <c r="G481" s="11" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>528.59</v>
       </c>
       <c r="F482" s="10" t="n">
-        <v>473.73</v>
+        <v>473.9</v>
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>80.68000000000001</v>
       </c>
       <c r="F483" s="10" t="n">
-        <v>80.84999999999999</v>
+        <v>80.86</v>
       </c>
       <c r="G483" s="11" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>983.1799999999999</v>
       </c>
       <c r="F484" s="10" t="n">
-        <v>977.73</v>
+        <v>980.33</v>
       </c>
       <c r="G484" s="11" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>1137.42</v>
       </c>
       <c r="F485" s="10" t="n">
-        <v>1029.57</v>
+        <v>1030.74</v>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>61.64</v>
       </c>
       <c r="F486" s="10" t="n">
-        <v>63.64</v>
+        <v>63.72</v>
       </c>
       <c r="G486" s="11" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>33564.08</v>
       </c>
       <c r="F487" s="10" t="n">
-        <v>33023.5</v>
+        <v>33026.96</v>
       </c>
       <c r="G487" s="11" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>188.85</v>
       </c>
       <c r="F488" s="10" t="n">
-        <v>230.42</v>
+        <v>230.63</v>
       </c>
       <c r="G488" s="11" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>23.85</v>
       </c>
       <c r="F490" s="10" t="n">
-        <v>25.11</v>
+        <v>25.12</v>
       </c>
       <c r="G490" s="11" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>2172.55</v>
       </c>
       <c r="F491" s="10" t="n">
-        <v>2282.08</v>
+        <v>2282.26</v>
       </c>
       <c r="G491" s="11" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>1315.86</v>
       </c>
       <c r="F492" s="10" t="n">
-        <v>1401.11</v>
+        <v>1400.64</v>
       </c>
       <c r="G492" s="11" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>586.83</v>
       </c>
       <c r="F493" s="10" t="n">
-        <v>639.24</v>
+        <v>639.4299999999999</v>
       </c>
       <c r="G493" s="11" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>4898.92</v>
       </c>
       <c r="F494" s="10" t="n">
-        <v>5174.45</v>
+        <v>5175.9</v>
       </c>
       <c r="G494" s="11" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>800.37</v>
       </c>
       <c r="F495" s="10" t="n">
-        <v>845.87</v>
+        <v>846.45</v>
       </c>
       <c r="G495" s="11" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>939.21</v>
       </c>
       <c r="F496" s="10" t="n">
-        <v>900.33</v>
+        <v>900.62</v>
       </c>
       <c r="G496" s="11" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>267</v>
       </c>
       <c r="F497" s="10" t="n">
-        <v>284.82</v>
+        <v>284.96</v>
       </c>
       <c r="G497" s="11" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>302.52</v>
       </c>
       <c r="F498" s="10" t="n">
-        <v>320.29</v>
+        <v>320.86</v>
       </c>
       <c r="G498" s="11" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>1460.17</v>
       </c>
       <c r="F499" s="10" t="n">
-        <v>1568.91</v>
+        <v>1570.41</v>
       </c>
       <c r="G499" s="11" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>3107.52</v>
       </c>
       <c r="F500" s="10" t="n">
-        <v>3071.4</v>
+        <v>3071.82</v>
       </c>
       <c r="G500" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Oct-2026  17:20:46    |    Closing Price Date: 09-Oct-2026</t>
+          <t>Scan Run: 12-Oct-2026  20:09:29    |    Closing Price Date: 09-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Oct-2026  17:20:46</t>
+          <t>12-Oct-2026  20:09:29</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         <v>1906.02</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1727.42</v>
+        <v>1726.23</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>725.88</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>793.67</v>
+        <v>793.7</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>1067.99</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1200.02</v>
+        <v>1200.7</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>563.71</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>501.45</v>
+        <v>501.38</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>1368.89</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.37</v>
+        <v>1360.7</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>366.57</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>300.4</v>
+        <v>300.62</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>3090.11</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3204.17</v>
+        <v>3205.03</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>1254.68</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1333.83</v>
+        <v>1334.81</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>422.41</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>396.37</v>
+        <v>396.51</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>1569.95</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1224.48</v>
+        <v>1225.15</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>2563.49</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2834.26</v>
+        <v>2832.12</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>265.18</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>292.62</v>
+        <v>292.4</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>4069.81</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3784.67</v>
+        <v>3783.75</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>2194.83</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2424.52</v>
+        <v>2424.04</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>7460.67</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7267.96</v>
+        <v>7266.29</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>1845</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1884.5</v>
+        <v>1884.54</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>1016.9</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>989.79</v>
+        <v>989.87</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>170.46</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>192.79</v>
+        <v>192.82</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>317.79</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>291.1</v>
+        <v>291.05</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>1783.66</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>1631.43</v>
+        <v>1632.09</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>416.74</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>413.69</v>
+        <v>413.58</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>2197.42</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>2262.74</v>
+        <v>2264.31</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>554.99</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>731.84</v>
+        <v>732.99</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>1745.28</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1657.17</v>
+        <v>1656.82</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         <v>11949.32</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>12570.83</v>
+        <v>12570.82</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>13418.16</v>
+        <v>13413.73</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>1247.36</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>1260.31</v>
+        <v>1260.35</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>3884.56</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3903.27</v>
+        <v>3902.61</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>3528.63</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>3931.1</v>
+        <v>3926.33</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>5265.52</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5179.01</v>
+        <v>5181.58</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>1000.31</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>1000.05</v>
+        <v>999.79</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>1546.49</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1506.52</v>
+        <v>1505.54</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         <v>5465.06</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>5425.01</v>
+        <v>5425</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>5371.15</v>
+        <v>5363.69</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>2509.2</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>2546.36</v>
+        <v>2547.37</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>396.63</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>409.88</v>
+        <v>409.45</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>782.96</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>655.61</v>
+        <v>655.37</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>386.81</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>451.37</v>
+        <v>451.21</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>3346.1</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3303.18</v>
+        <v>3298.13</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>13443.23</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>13089.65</v>
+        <v>13101.46</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         <v>1353.17</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>1392.38</v>
+        <v>1392.39</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1362.09</v>
+        <v>1363.04</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>1015.93</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>971.8</v>
+        <v>971.5599999999999</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>397.92</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>353.61</v>
+        <v>353.84</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>1971.01</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2133.48</v>
+        <v>2137.9</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44.16</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>49.64</v>
+        <v>49.69</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>269.21</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>298.12</v>
+        <v>298.25</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>8902.049999999999</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>7546.51</v>
+        <v>7547.74</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>1252.7</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1309.18</v>
+        <v>1308.84</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>1143.66</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1092.18</v>
+        <v>1091.27</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>411.13</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>403.04</v>
+        <v>402.88</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>170.11</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>164.59</v>
+        <v>164.65</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>323.53</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>315.41</v>
+        <v>314.92</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>4337.72</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>4066.59</v>
+        <v>4064.94</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>1860.91</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>1818.09</v>
+        <v>1818.43</v>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>295.9</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>291.41</v>
+        <v>290.9</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>202.9</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>186.87</v>
+        <v>186.8</v>
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>1883.26</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>1478.63</v>
+        <v>1479.47</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>980.4</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>954.72</v>
+        <v>954.45</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>3813.3</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>4008.37</v>
+        <v>4001.64</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>225.85</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>167.27</v>
+        <v>167.17</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         <v>2857.08</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>2924.11</v>
+        <v>2924.1</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>2728.77</v>
+        <v>2726.43</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>4849.07</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4488.95</v>
+        <v>4489.07</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>230.7</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>250.21</v>
+        <v>250.27</v>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>4772.31</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4449.86</v>
+        <v>4448.06</v>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>1379.88</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>1129.54</v>
+        <v>1131.05</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>17528.71</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>18408.32</v>
+        <v>18419.64</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>3166.7</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>2774.19</v>
+        <v>2772.55</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>1616.26</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1354.1</v>
+        <v>1353.84</v>
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>204.82</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>191.41</v>
+        <v>191.46</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>31970.52</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>29406.54</v>
+        <v>29388.93</v>
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>883.88</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>826.26</v>
+        <v>826.88</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>11141.77</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>11451.09</v>
+        <v>11447.2</v>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>330.24</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>344.03</v>
+        <v>344.19</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>1077.35</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>1112.64</v>
+        <v>1114.02</v>
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>11029.78</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>10301.49</v>
+        <v>10306.06</v>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>354.45</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>383.59</v>
+        <v>383.31</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>1399.44</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1382.44</v>
+        <v>1376.9</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>8574.32</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>8422.139999999999</v>
+        <v>8419.18</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>327.4</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>313.38</v>
+        <v>313.36</v>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>435.05</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>457.33</v>
+        <v>457.81</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>1450.92</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>1104.99</v>
+        <v>1104.69</v>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>4390.4</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>3767.18</v>
+        <v>3772.18</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>417.22</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>411.31</v>
+        <v>410.9</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>84.58</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>93.18000000000001</v>
+        <v>93.34</v>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>2859.82</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>3088.63</v>
+        <v>3090.14</v>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>13.8</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4591,10 +4591,10 @@
         <v>4943.77</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>5004.79</v>
+        <v>5004.78</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>5022.72</v>
+        <v>5013.82</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>329.95</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>294.82</v>
+        <v>294.39</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>1753.19</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1830.93</v>
+        <v>1828.86</v>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>234.37</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>245.83</v>
+        <v>245.85</v>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
@@ -4767,10 +4767,10 @@
         <v>4740.38</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>4740.49</v>
+        <v>4740.5</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>4553.26</v>
+        <v>4558.14</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>4768.42</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>4164.7</v>
+        <v>4161.97</v>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>2296.05</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>2464.28</v>
+        <v>2464.19</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>2141.93</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>2197.66</v>
+        <v>2198.1</v>
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>184.8</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>186.86</v>
+        <v>186.71</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>679.23</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>614.0599999999999</v>
+        <v>613.9299999999999</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>272.68</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>381.36</v>
+        <v>380.73</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>2884.33</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>2530.02</v>
+        <v>2529.98</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>11116.38</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>9888.799999999999</v>
+        <v>9891.32</v>
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>43.9</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>43.67</v>
+        <v>43.57</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>7156.55</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>6677.37</v>
+        <v>6674.74</v>
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>2830.81</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>3165.63</v>
+        <v>3134.39</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>544.6799999999999</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>606.12</v>
+        <v>606.11</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>393.11</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>431.66</v>
+        <v>432.72</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>2325.44</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2382.56</v>
+        <v>2381.97</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>76.08</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>69.88</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>356.17</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>374.29</v>
+        <v>374.74</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>420.93</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>365.7</v>
+        <v>365.52</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>8578.219999999999</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8223.690000000001</v>
+        <v>8231.209999999999</v>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>160.85</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>160.82</v>
+        <v>160.78</v>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>379.14</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>389.46</v>
+        <v>388.83</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>602.33</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>550.72</v>
+        <v>551.79</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>1642.63</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1500.6</v>
+        <v>1498.31</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>239.38</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>253.48</v>
+        <v>253.4</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>1424.24</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1325.31</v>
+        <v>1325.52</v>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>266.61</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>278.38</v>
+        <v>278.43</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>956.38</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>973.48</v>
+        <v>972.86</v>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>4414.48</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>3938.91</v>
+        <v>3939.29</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>2623.6</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>2782.42</v>
+        <v>2780.05</v>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>334.6</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>306.21</v>
+        <v>306.1</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>347.9</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>332.57</v>
+        <v>332.83</v>
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>357.98</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>347.86</v>
+        <v>347.7</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>3271.5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>3208.25</v>
+        <v>3210.43</v>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>4233.04</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>4503.84</v>
+        <v>4505.79</v>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>1735.83</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>1694.85</v>
+        <v>1693.11</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>408.91</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>340.05</v>
+        <v>340.25</v>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>392.04</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>395.01</v>
+        <v>395.18</v>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>307.23</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>315.06</v>
+        <v>315.82</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>1414.78</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1383.13</v>
+        <v>1383.1</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>147.65</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>138.65</v>
+        <v>138.53</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>1139.55</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1249</v>
+        <v>1248.42</v>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>307.62</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>363.94</v>
+        <v>363.95</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>264.61</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>272.43</v>
+        <v>272.65</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>176.87</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>166.82</v>
+        <v>166.65</v>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>745.24</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>705.02</v>
+        <v>704.96</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>16998.04</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>13733.6</v>
+        <v>13720.77</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>132.11</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>129.81</v>
+        <v>130.08</v>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>2833.15</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>2350.6</v>
+        <v>2350.94</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>366.85</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>426.87</v>
+        <v>427.19</v>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>1016.76</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1081.43</v>
+        <v>1081.7</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>599.0599999999999</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>568.16</v>
+        <v>567.74</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>1003.04</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1049.43</v>
+        <v>1050.13</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>1558.24</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>1523.29</v>
+        <v>1523.19</v>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>5331.75</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>5392.66</v>
+        <v>5392.79</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>570.08</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>556.58</v>
+        <v>556.61</v>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>817.33</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>798.5700000000001</v>
+        <v>799.29</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>722.59</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>706.29</v>
+        <v>705.48</v>
       </c>
       <c r="G152" s="11" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>4892.58</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>4818.15</v>
+        <v>4819.97</v>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>1513.2</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1519.07</v>
+        <v>1520.33</v>
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>1314.11</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>1247.8</v>
+        <v>1246.6</v>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>82.87</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>78.73999999999999</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="G156" s="11" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>19625.2</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>17451.75</v>
+        <v>17442.04</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>175.14</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>176.9</v>
+        <v>176.46</v>
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>18.69</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>20.24</v>
+        <v>20.23</v>
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>340.07</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>310.23</v>
+        <v>310.01</v>
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>5084.29</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>4944.97</v>
+        <v>4949.16</v>
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>176.34</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>168.93</v>
+        <v>168.88</v>
       </c>
       <c r="G162" s="11" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>572.46</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>559.99</v>
+        <v>559.5700000000001</v>
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>10480.65</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>9045.139999999999</v>
+        <v>9050.73</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>1196.16</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>1229.3</v>
+        <v>1230.99</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>656.98</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>650.78</v>
+        <v>650.8</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>318.17</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>337.83</v>
+        <v>337.68</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>558.85</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>528.5700000000001</v>
+        <v>528.66</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>822.4400000000001</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>859.35</v>
+        <v>859.72</v>
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>2086.74</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>2071.88</v>
+        <v>2070.95</v>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>1098.86</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>1106.25</v>
+        <v>1109.51</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>1858.53</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1891.57</v>
+        <v>1891.52</v>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>37007.83</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>37702.6</v>
+        <v>37762.85</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>5074.57</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>5365.03</v>
+        <v>5369.03</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>74.18000000000001</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>93.12</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>82.48999999999999</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>96.34999999999999</v>
+        <v>96.27</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>3494.69</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>3164.28</v>
+        <v>3168.87</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>158.88</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>140.43</v>
+        <v>140.5</v>
       </c>
       <c r="G178" s="11" t="inlineStr">
         <is>
@@ -8541,17 +8541,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>237.17</v>
+        <v>233.56</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>291.86</v>
+        <v>286.3</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>418.31</v>
+        <v>411.07</v>
       </c>
       <c r="F179" s="10" t="n">
         <v/>
@@ -8598,7 +8598,7 @@
         <v>3418.59</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>4096.26</v>
+        <v>4095.81</v>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>2557.11</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>2111.23</v>
+        <v>2110.46</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>1483.49</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>1575.1</v>
+        <v>1571.83</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>7115.97</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>7315.98</v>
+        <v>7324.9</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>1036.2</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>995.29</v>
+        <v>995.14</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>1875.56</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>2012.11</v>
+        <v>2013.42</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>222.69</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>206.27</v>
+        <v>206.19</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>437.41</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>445.52</v>
+        <v>445.94</v>
       </c>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>522.6</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>561.38</v>
+        <v>560.77</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>22.2</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>22.03</v>
+        <v>22.02</v>
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>1245.41</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>1196.67</v>
+        <v>1195.75</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>950.92</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>925.51</v>
+        <v>925.36</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>1384.66</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>1397.85</v>
+        <v>1398.4</v>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>8253.48</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>7228.73</v>
+        <v>7229.44</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>2001.63</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>2219.29</v>
+        <v>2214.8</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>3237</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2772.78</v>
+        <v>2774.25</v>
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>16.18</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>17.15</v>
+        <v>17.32</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>1499.19</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>1620.77</v>
+        <v>1620.93</v>
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>896.17</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>941.42</v>
+        <v>938.9299999999999</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>1265.28</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>1231.45</v>
+        <v>1230.71</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>1650.03</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>1471.87</v>
+        <v>1473.05</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>1892.72</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>1685.71</v>
+        <v>1687.47</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>114.17</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>111.97</v>
+        <v>111.91</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9651,10 +9651,10 @@
         <v>46015.73</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>45639.7</v>
+        <v>45639.71</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>40777.01</v>
+        <v>40928.95</v>
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>502.87</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>488.7</v>
+        <v>488.31</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>813.02</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>881.03</v>
+        <v>880.41</v>
       </c>
       <c r="G206" s="11" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>393.34</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>446.45</v>
+        <v>446.35</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>1798.22</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>1879.98</v>
+        <v>1880.37</v>
       </c>
       <c r="G208" s="11" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>1394.24</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>1503.32</v>
+        <v>1504.46</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>79.98</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>80.59999999999999</v>
+        <v>80.61</v>
       </c>
       <c r="G210" s="11" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>1324.5</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1355.7</v>
+        <v>1355.68</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>21662.67</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>18325.14</v>
+        <v>18316.68</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>2392.98</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>2541.92</v>
+        <v>2538.41</v>
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>1243.39</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>1075.17</v>
+        <v>1072.63</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>456.43</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>531.77</v>
+        <v>531.87</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>365.5</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>381.84</v>
+        <v>381.6</v>
       </c>
       <c r="G216" s="11" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>496.2</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>571.23</v>
+        <v>570.28</v>
       </c>
       <c r="G217" s="11" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>2348.46</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>2218.18</v>
+        <v>2222.07</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>278.01</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>293.55</v>
+        <v>294.03</v>
       </c>
       <c r="G219" s="11" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>171.82</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>169.17</v>
+        <v>169.27</v>
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>135.45</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>141.63</v>
+        <v>141.87</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>51.22</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>60.74</v>
+        <v>60.75</v>
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>1841.69</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>1681.18</v>
+        <v>1681.32</v>
       </c>
       <c r="G223" s="11" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>763.58</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>742.35</v>
+        <v>743.35</v>
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>542.91</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>562.66</v>
+        <v>563.23</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>97.86</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>99.03</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>2553.68</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>2685.87</v>
+        <v>2685.19</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>1121.18</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>1033.23</v>
+        <v>1033.38</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>3141.34</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>3025.17</v>
+        <v>3022.13</v>
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>1375.88</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1370.14</v>
+        <v>1370.88</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10883,10 +10883,10 @@
         <v>1893.57</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>1908.5</v>
+        <v>1908.51</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>1826.18</v>
+        <v>1828.55</v>
       </c>
       <c r="G232" s="11" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>2100.8</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>1967.29</v>
+        <v>1966.91</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>1140.21</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>1058.32</v>
+        <v>1058.46</v>
       </c>
       <c r="G234" s="11" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>294.2</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>287.11</v>
+        <v>287.18</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>1435.61</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>1476.15</v>
+        <v>1475.91</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>761.23</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>682.3</v>
+        <v>681.96</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>38.06</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>38.37</v>
+        <v>38.39</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>534.9400000000001</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>533.66</v>
+        <v>533.6</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>2045.81</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>1783.8</v>
+        <v>1784.02</v>
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>288.03</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>327.54</v>
+        <v>327.16</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>990.12</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>909.85</v>
+        <v>913.02</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>3822.14</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>3597.33</v>
+        <v>3596.9</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>1165.24</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>1280.87</v>
+        <v>1282.28</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>2418.65</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>2368.57</v>
+        <v>2369.68</v>
       </c>
       <c r="G247" s="11" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>1188.16</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>1171.78</v>
+        <v>1171.57</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>2444.12</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>2543.8</v>
+        <v>2542.17</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>138.39</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>139.4</v>
+        <v>139.34</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>328.82</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>301.26</v>
+        <v>301.14</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>465.03</v>
       </c>
       <c r="F252" s="10" t="n">
-        <v>455.03</v>
+        <v>455.22</v>
       </c>
       <c r="G252" s="11" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>270.28</v>
       </c>
       <c r="F253" s="10" t="n">
-        <v>278.57</v>
+        <v>278.39</v>
       </c>
       <c r="G253" s="11" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>1114.38</v>
       </c>
       <c r="F255" s="10" t="n">
-        <v>1112.74</v>
+        <v>1112.09</v>
       </c>
       <c r="G255" s="11" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>1618.69</v>
       </c>
       <c r="F256" s="10" t="n">
-        <v>1668.28</v>
+        <v>1667.29</v>
       </c>
       <c r="G256" s="11" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>618.5</v>
       </c>
       <c r="F257" s="10" t="n">
-        <v>681.2</v>
+        <v>681.02</v>
       </c>
       <c r="G257" s="11" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>1584.82</v>
       </c>
       <c r="F258" s="10" t="n">
-        <v>1728.13</v>
+        <v>1727.32</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>1283.79</v>
       </c>
       <c r="F259" s="10" t="n">
-        <v>1364.86</v>
+        <v>1363.65</v>
       </c>
       <c r="G259" s="11" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1201.36</v>
       </c>
       <c r="F260" s="10" t="n">
-        <v>1328.24</v>
+        <v>1326.85</v>
       </c>
       <c r="G260" s="11" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>404.44</v>
       </c>
       <c r="F261" s="10" t="n">
-        <v>412.03</v>
+        <v>411.73</v>
       </c>
       <c r="G261" s="11" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>1133.16</v>
       </c>
       <c r="F262" s="10" t="n">
-        <v>1051.76</v>
+        <v>1051.28</v>
       </c>
       <c r="G262" s="11" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>560.1799999999999</v>
       </c>
       <c r="F263" s="10" t="n">
-        <v>547.13</v>
+        <v>549.75</v>
       </c>
       <c r="G263" s="11" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>1977.83</v>
       </c>
       <c r="F264" s="10" t="n">
-        <v>1856.5</v>
+        <v>1856.54</v>
       </c>
       <c r="G264" s="11" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>841.45</v>
       </c>
       <c r="F265" s="10" t="n">
-        <v>830.8099999999999</v>
+        <v>830.53</v>
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>211.69</v>
       </c>
       <c r="F266" s="10" t="n">
-        <v>256.62</v>
+        <v>256.49</v>
       </c>
       <c r="G266" s="11" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>115.39</v>
       </c>
       <c r="F267" s="10" t="n">
-        <v>126.03</v>
+        <v>126.2</v>
       </c>
       <c r="G267" s="11" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>844.76</v>
       </c>
       <c r="F268" s="10" t="n">
-        <v>745.52</v>
+        <v>745.63</v>
       </c>
       <c r="G268" s="11" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>7303.12</v>
       </c>
       <c r="F269" s="10" t="n">
-        <v>7851.51</v>
+        <v>7855.1</v>
       </c>
       <c r="G269" s="11" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>217.39</v>
       </c>
       <c r="F270" s="10" t="n">
-        <v>216.2</v>
+        <v>216.83</v>
       </c>
       <c r="G270" s="11" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>83.87</v>
       </c>
       <c r="F271" s="10" t="n">
-        <v>89.11</v>
+        <v>89.09</v>
       </c>
       <c r="G271" s="11" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>82</v>
       </c>
       <c r="F272" s="10" t="n">
-        <v>75.53</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>481.24</v>
       </c>
       <c r="F273" s="10" t="n">
-        <v>531.55</v>
+        <v>531.88</v>
       </c>
       <c r="G273" s="11" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>470.58</v>
       </c>
       <c r="F274" s="10" t="n">
-        <v>475.93</v>
+        <v>477.16</v>
       </c>
       <c r="G274" s="11" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>520.5599999999999</v>
       </c>
       <c r="F275" s="10" t="n">
-        <v>528.09</v>
+        <v>527.73</v>
       </c>
       <c r="G275" s="11" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>479.1</v>
       </c>
       <c r="F276" s="10" t="n">
-        <v>494.59</v>
+        <v>494.67</v>
       </c>
       <c r="G276" s="11" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>2170.03</v>
       </c>
       <c r="F277" s="10" t="n">
-        <v>1821.17</v>
+        <v>1821.18</v>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>248.07</v>
       </c>
       <c r="F278" s="10" t="n">
-        <v>217.32</v>
+        <v>217.25</v>
       </c>
       <c r="G278" s="11" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>105.05</v>
       </c>
       <c r="F279" s="10" t="n">
-        <v>115.61</v>
+        <v>115.43</v>
       </c>
       <c r="G279" s="11" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>34975.09</v>
       </c>
       <c r="F280" s="10" t="n">
-        <v>34941.88</v>
+        <v>35023.33</v>
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>910.6</v>
       </c>
       <c r="F281" s="10" t="n">
-        <v>1018.53</v>
+        <v>1022.53</v>
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>2697.73</v>
       </c>
       <c r="F282" s="10" t="n">
-        <v>2665.09</v>
+        <v>2656.31</v>
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>84.54000000000001</v>
       </c>
       <c r="F283" s="10" t="n">
-        <v>86.45</v>
+        <v>86.38</v>
       </c>
       <c r="G283" s="11" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>230.23</v>
       </c>
       <c r="F284" s="10" t="n">
-        <v>254.63</v>
+        <v>254.82</v>
       </c>
       <c r="G284" s="11" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>694.83</v>
       </c>
       <c r="F285" s="10" t="n">
-        <v>624.9400000000001</v>
+        <v>624.72</v>
       </c>
       <c r="G285" s="11" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>753.71</v>
       </c>
       <c r="F286" s="10" t="n">
-        <v>725.86</v>
+        <v>727.0700000000001</v>
       </c>
       <c r="G286" s="11" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>1701.11</v>
       </c>
       <c r="F287" s="10" t="n">
-        <v>1657.95</v>
+        <v>1657.36</v>
       </c>
       <c r="G287" s="11" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>1320.15</v>
       </c>
       <c r="F288" s="10" t="n">
-        <v>1046.45</v>
+        <v>1047</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>875.6</v>
       </c>
       <c r="F289" s="10" t="n">
-        <v>941.5700000000001</v>
+        <v>941.45</v>
       </c>
       <c r="G289" s="11" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>235.95</v>
       </c>
       <c r="F290" s="10" t="n">
-        <v>211.13</v>
+        <v>211.12</v>
       </c>
       <c r="G290" s="11" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>513.73</v>
       </c>
       <c r="F291" s="10" t="n">
-        <v>513.7</v>
+        <v>513.35</v>
       </c>
       <c r="G291" s="11" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>1486.85</v>
       </c>
       <c r="F292" s="10" t="n">
-        <v>1614.5</v>
+        <v>1611.21</v>
       </c>
       <c r="G292" s="11" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>3710.5</v>
       </c>
       <c r="F293" s="10" t="n">
-        <v>3819.27</v>
+        <v>3821.32</v>
       </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>286.33</v>
       </c>
       <c r="F294" s="10" t="n">
-        <v>280.65</v>
+        <v>281.01</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>84.78</v>
       </c>
       <c r="F295" s="10" t="n">
-        <v>94.51000000000001</v>
+        <v>94.33</v>
       </c>
       <c r="G295" s="11" t="inlineStr">
         <is>
@@ -13699,10 +13699,10 @@
         <v>124848.59</v>
       </c>
       <c r="E296" s="10" t="n">
-        <v>127581.94</v>
+        <v>127581.93</v>
       </c>
       <c r="F296" s="10" t="n">
-        <v>133610.98</v>
+        <v>133520.33</v>
       </c>
       <c r="G296" s="11" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>522.91</v>
       </c>
       <c r="F297" s="10" t="n">
-        <v>519.47</v>
+        <v>519.8099999999999</v>
       </c>
       <c r="G297" s="11" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>1548.35</v>
       </c>
       <c r="F298" s="10" t="n">
-        <v>1583.94</v>
+        <v>1584.68</v>
       </c>
       <c r="G298" s="11" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>75.55</v>
       </c>
       <c r="F299" s="10" t="n">
-        <v>77.45999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="G299" s="11" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>467.13</v>
       </c>
       <c r="F300" s="10" t="n">
-        <v>490.18</v>
+        <v>489.11</v>
       </c>
       <c r="G300" s="11" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>723.86</v>
       </c>
       <c r="F301" s="10" t="n">
-        <v>744.71</v>
+        <v>743.95</v>
       </c>
       <c r="G301" s="11" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>1240.38</v>
       </c>
       <c r="F303" s="10" t="n">
-        <v>1135.6</v>
+        <v>1135.33</v>
       </c>
       <c r="G303" s="11" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>540.05</v>
       </c>
       <c r="F304" s="10" t="n">
-        <v>559.71</v>
+        <v>558.86</v>
       </c>
       <c r="G304" s="11" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>1046.74</v>
       </c>
       <c r="F305" s="10" t="n">
-        <v>959.83</v>
+        <v>959.5599999999999</v>
       </c>
       <c r="G305" s="11" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>146.31</v>
       </c>
       <c r="F306" s="10" t="n">
-        <v>151.91</v>
+        <v>151.39</v>
       </c>
       <c r="G306" s="11" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>603.0599999999999</v>
       </c>
       <c r="F307" s="10" t="n">
-        <v>623.67</v>
+        <v>623.1799999999999</v>
       </c>
       <c r="G307" s="11" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>91.45</v>
       </c>
       <c r="F308" s="10" t="n">
-        <v>95.37</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>972.9299999999999</v>
       </c>
       <c r="F309" s="10" t="n">
-        <v>878.9400000000001</v>
+        <v>878.15</v>
       </c>
       <c r="G309" s="11" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>556.63</v>
       </c>
       <c r="F310" s="10" t="n">
-        <v>613.22</v>
+        <v>613.54</v>
       </c>
       <c r="G310" s="11" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>391.05</v>
       </c>
       <c r="F311" s="10" t="n">
-        <v>366.95</v>
+        <v>367.06</v>
       </c>
       <c r="G311" s="11" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>3482.43</v>
       </c>
       <c r="F312" s="10" t="n">
-        <v>3593.12</v>
+        <v>3591.91</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>1350.94</v>
       </c>
       <c r="F313" s="10" t="n">
-        <v>1208.87</v>
+        <v>1206.51</v>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>10925.19</v>
       </c>
       <c r="F314" s="10" t="n">
-        <v>10959.48</v>
+        <v>10954.15</v>
       </c>
       <c r="G314" s="11" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>1436.78</v>
       </c>
       <c r="F315" s="10" t="n">
-        <v>1341.03</v>
+        <v>1342</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>1030.59</v>
       </c>
       <c r="F316" s="10" t="n">
-        <v>995.12</v>
+        <v>995.75</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>1213.3</v>
       </c>
       <c r="F317" s="10" t="n">
-        <v>1097.48</v>
+        <v>1098.08</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>1489.63</v>
       </c>
       <c r="F318" s="10" t="n">
-        <v>1228.21</v>
+        <v>1228.41</v>
       </c>
       <c r="G318" s="11" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>1851.34</v>
       </c>
       <c r="F319" s="10" t="n">
-        <v>1794.66</v>
+        <v>1794.11</v>
       </c>
       <c r="G319" s="11" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>661.9</v>
       </c>
       <c r="F320" s="10" t="n">
-        <v>754.6</v>
+        <v>754.9299999999999</v>
       </c>
       <c r="G320" s="11" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>3394.97</v>
       </c>
       <c r="F321" s="10" t="n">
-        <v>3487.48</v>
+        <v>3486.25</v>
       </c>
       <c r="G321" s="11" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>2372.94</v>
       </c>
       <c r="F322" s="10" t="n">
-        <v>1636.44</v>
+        <v>1635.78</v>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>457.74</v>
       </c>
       <c r="F323" s="10" t="n">
-        <v>450.31</v>
+        <v>450.47</v>
       </c>
       <c r="G323" s="11" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>1542.78</v>
       </c>
       <c r="F324" s="10" t="n">
-        <v>1650.47</v>
+        <v>1653.46</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>113.35</v>
       </c>
       <c r="F325" s="10" t="n">
-        <v>124.08</v>
+        <v>124.04</v>
       </c>
       <c r="G325" s="11" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>4473.46</v>
       </c>
       <c r="F326" s="10" t="n">
-        <v>4012.57</v>
+        <v>4011.34</v>
       </c>
       <c r="G326" s="11" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>620.76</v>
       </c>
       <c r="F327" s="10" t="n">
-        <v>630.35</v>
+        <v>630.0599999999999</v>
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>414.08</v>
       </c>
       <c r="F328" s="10" t="n">
-        <v>528.01</v>
+        <v>527.34</v>
       </c>
       <c r="G328" s="11" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>160.97</v>
       </c>
       <c r="F329" s="10" t="n">
-        <v>171.76</v>
+        <v>171.57</v>
       </c>
       <c r="G329" s="11" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>562.6799999999999</v>
       </c>
       <c r="F330" s="10" t="n">
-        <v>606.88</v>
+        <v>607.71</v>
       </c>
       <c r="G330" s="11" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>2411.75</v>
       </c>
       <c r="F331" s="10" t="n">
-        <v>2821.47</v>
+        <v>2821.17</v>
       </c>
       <c r="G331" s="11" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>1705.31</v>
       </c>
       <c r="F332" s="10" t="n">
-        <v>1933.31</v>
+        <v>1932</v>
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>262.32</v>
       </c>
       <c r="F333" s="10" t="n">
-        <v>295.37</v>
+        <v>295.16</v>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>1397.26</v>
       </c>
       <c r="F334" s="10" t="n">
-        <v>1299</v>
+        <v>1300.58</v>
       </c>
       <c r="G334" s="11" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>1738.62</v>
       </c>
       <c r="F335" s="10" t="n">
-        <v>1862.47</v>
+        <v>1859.63</v>
       </c>
       <c r="G335" s="11" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>6248.44</v>
       </c>
       <c r="F336" s="10" t="n">
-        <v>6423.49</v>
+        <v>6433.41</v>
       </c>
       <c r="G336" s="11" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>1721.71</v>
       </c>
       <c r="F338" s="10" t="n">
-        <v>1727.16</v>
+        <v>1725.5</v>
       </c>
       <c r="G338" s="11" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>1291.06</v>
       </c>
       <c r="F339" s="10" t="n">
-        <v>1389.64</v>
+        <v>1394.08</v>
       </c>
       <c r="G339" s="11" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>873.01</v>
       </c>
       <c r="F340" s="10" t="n">
-        <v>904.4</v>
+        <v>904.98</v>
       </c>
       <c r="G340" s="11" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>1794.04</v>
       </c>
       <c r="F341" s="10" t="n">
-        <v>1738.33</v>
+        <v>1736.03</v>
       </c>
       <c r="G341" s="11" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>738.34</v>
       </c>
       <c r="F342" s="10" t="n">
-        <v>749.36</v>
+        <v>749.79</v>
       </c>
       <c r="G342" s="11" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>2400.7</v>
       </c>
       <c r="F343" s="10" t="n">
-        <v>2410.87</v>
+        <v>2410.54</v>
       </c>
       <c r="G343" s="11" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>2129.25</v>
       </c>
       <c r="F344" s="10" t="n">
-        <v>1867.73</v>
+        <v>1867.75</v>
       </c>
       <c r="G344" s="11" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>461.29</v>
       </c>
       <c r="F345" s="10" t="n">
-        <v>397.43</v>
+        <v>397.47</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>576.12</v>
       </c>
       <c r="F346" s="10" t="n">
-        <v>538.22</v>
+        <v>538.14</v>
       </c>
       <c r="G346" s="11" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>3356.02</v>
       </c>
       <c r="F347" s="10" t="n">
-        <v>3548.17</v>
+        <v>3550.48</v>
       </c>
       <c r="G347" s="11" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>937.34</v>
       </c>
       <c r="F348" s="10" t="n">
-        <v>1093.93</v>
+        <v>1095.28</v>
       </c>
       <c r="G348" s="11" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>21.81</v>
       </c>
       <c r="F349" s="10" t="n">
-        <v>28.11</v>
+        <v>27.99</v>
       </c>
       <c r="G349" s="11" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>1219.86</v>
       </c>
       <c r="F350" s="10" t="n">
-        <v>1253.66</v>
+        <v>1252.9</v>
       </c>
       <c r="G350" s="11" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>1564.7</v>
       </c>
       <c r="F351" s="10" t="n">
-        <v>1624.23</v>
+        <v>1623.58</v>
       </c>
       <c r="G351" s="11" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>661.95</v>
       </c>
       <c r="F352" s="10" t="n">
-        <v>693.37</v>
+        <v>693.49</v>
       </c>
       <c r="G352" s="11" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>23370.54</v>
       </c>
       <c r="F353" s="10" t="n">
-        <v>25244.39</v>
+        <v>25221.4</v>
       </c>
       <c r="G353" s="11" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>1208.5</v>
       </c>
       <c r="F354" s="10" t="n">
-        <v>1145.74</v>
+        <v>1147.73</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>177.66</v>
       </c>
       <c r="F355" s="10" t="n">
-        <v>193.58</v>
+        <v>193.3</v>
       </c>
       <c r="G355" s="11" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>36.36</v>
       </c>
       <c r="F356" s="10" t="n">
-        <v>39.18</v>
+        <v>39.25</v>
       </c>
       <c r="G356" s="11" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>238.33</v>
       </c>
       <c r="F358" s="10" t="n">
-        <v>270.29</v>
+        <v>269.98</v>
       </c>
       <c r="G358" s="11" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>419.11</v>
       </c>
       <c r="F359" s="10" t="n">
-        <v>443.97</v>
+        <v>444.29</v>
       </c>
       <c r="G359" s="11" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>474.86</v>
       </c>
       <c r="F361" s="10" t="n">
-        <v>540.48</v>
+        <v>540.85</v>
       </c>
       <c r="G361" s="11" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>283.69</v>
       </c>
       <c r="F362" s="10" t="n">
-        <v>272.56</v>
+        <v>272.73</v>
       </c>
       <c r="G362" s="11" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>680.88</v>
       </c>
       <c r="F363" s="10" t="n">
-        <v>629.74</v>
+        <v>629.9400000000001</v>
       </c>
       <c r="G363" s="11" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>1899.33</v>
       </c>
       <c r="F365" s="10" t="n">
-        <v>1687.93</v>
+        <v>1691.53</v>
       </c>
       <c r="G365" s="11" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>298.08</v>
       </c>
       <c r="F367" s="10" t="n">
-        <v>266.68</v>
+        <v>266.6</v>
       </c>
       <c r="G367" s="11" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>416.72</v>
       </c>
       <c r="F368" s="10" t="n">
-        <v>433.3</v>
+        <v>433.03</v>
       </c>
       <c r="G368" s="11" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>267.27</v>
       </c>
       <c r="F369" s="10" t="n">
-        <v>310.04</v>
+        <v>309.74</v>
       </c>
       <c r="G369" s="11" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>490.31</v>
       </c>
       <c r="F370" s="10" t="n">
-        <v>466.19</v>
+        <v>465.43</v>
       </c>
       <c r="G370" s="11" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>1850.8</v>
       </c>
       <c r="F372" s="10" t="n">
-        <v>1865.8</v>
+        <v>1866.17</v>
       </c>
       <c r="G372" s="11" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>5112.49</v>
       </c>
       <c r="F373" s="10" t="n">
-        <v>5407.77</v>
+        <v>5411.43</v>
       </c>
       <c r="G373" s="11" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>1950.79</v>
       </c>
       <c r="F374" s="10" t="n">
-        <v>1866.92</v>
+        <v>1871.46</v>
       </c>
       <c r="G374" s="11" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>291.98</v>
       </c>
       <c r="F375" s="10" t="n">
-        <v>337.38</v>
+        <v>337.66</v>
       </c>
       <c r="G375" s="11" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>1258.48</v>
       </c>
       <c r="F376" s="10" t="n">
-        <v>1423.45</v>
+        <v>1424.52</v>
       </c>
       <c r="G376" s="11" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>4119.04</v>
       </c>
       <c r="F377" s="10" t="n">
-        <v>4074.99</v>
+        <v>4079.26</v>
       </c>
       <c r="G377" s="11" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>1417.51</v>
       </c>
       <c r="F378" s="10" t="n">
-        <v>1358.55</v>
+        <v>1358.72</v>
       </c>
       <c r="G378" s="11" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>852.87</v>
       </c>
       <c r="F379" s="10" t="n">
-        <v>912.48</v>
+        <v>914.67</v>
       </c>
       <c r="G379" s="11" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>145.43</v>
       </c>
       <c r="F380" s="10" t="n">
-        <v>155.6</v>
+        <v>155.74</v>
       </c>
       <c r="G380" s="11" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>852.3099999999999</v>
       </c>
       <c r="F381" s="10" t="n">
-        <v>841.1799999999999</v>
+        <v>840.01</v>
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>1737.81</v>
       </c>
       <c r="F382" s="10" t="n">
-        <v>1604.3</v>
+        <v>1599.45</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>1084.41</v>
       </c>
       <c r="F383" s="10" t="n">
-        <v>1066.75</v>
+        <v>1068.28</v>
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>1159.76</v>
       </c>
       <c r="F384" s="10" t="n">
-        <v>1160.98</v>
+        <v>1162.82</v>
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>235.29</v>
       </c>
       <c r="F385" s="10" t="n">
-        <v>248.69</v>
+        <v>248.63</v>
       </c>
       <c r="G385" s="11" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>1270.96</v>
       </c>
       <c r="F386" s="10" t="n">
-        <v>1426.23</v>
+        <v>1428.38</v>
       </c>
       <c r="G386" s="11" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>2623.31</v>
       </c>
       <c r="F387" s="10" t="n">
-        <v>2290.87</v>
+        <v>2293.99</v>
       </c>
       <c r="G387" s="11" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>731.92</v>
       </c>
       <c r="F388" s="10" t="n">
-        <v>733.63</v>
+        <v>732.42</v>
       </c>
       <c r="G388" s="11" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>467.68</v>
       </c>
       <c r="F389" s="10" t="n">
-        <v>481.33</v>
+        <v>480.89</v>
       </c>
       <c r="G389" s="11" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>650.79</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>586.55</v>
+        <v>586.99</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>186.49</v>
       </c>
       <c r="F391" s="10" t="n">
-        <v>200.06</v>
+        <v>200.05</v>
       </c>
       <c r="G391" s="11" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>361.38</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>393.48</v>
+        <v>393.55</v>
       </c>
       <c r="G392" s="11" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>1396.96</v>
       </c>
       <c r="F393" s="10" t="n">
-        <v>1381.04</v>
+        <v>1383.41</v>
       </c>
       <c r="G393" s="11" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>998.29</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>1073.87</v>
+        <v>1080.64</v>
       </c>
       <c r="G394" s="11" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>328.3</v>
       </c>
       <c r="F395" s="10" t="n">
-        <v>337.34</v>
+        <v>338.48</v>
       </c>
       <c r="G395" s="11" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>3976.76</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>4011.18</v>
+        <v>4009.08</v>
       </c>
       <c r="G396" s="11" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>24.46</v>
       </c>
       <c r="F397" s="10" t="n">
-        <v>26.3</v>
+        <v>26.28</v>
       </c>
       <c r="G397" s="11" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>284.84</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>254.03</v>
+        <v>254.31</v>
       </c>
       <c r="G398" s="11" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>1631.65</v>
       </c>
       <c r="F399" s="10" t="n">
-        <v>1663.58</v>
+        <v>1662.95</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>292.19</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>317.95</v>
+        <v>318.78</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>650.97</v>
       </c>
       <c r="F401" s="10" t="n">
-        <v>709.05</v>
+        <v>708.83</v>
       </c>
       <c r="G401" s="11" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>756.9</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>749.24</v>
+        <v>749.96</v>
       </c>
       <c r="G402" s="11" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>649.0700000000001</v>
       </c>
       <c r="F403" s="10" t="n">
-        <v>667.9299999999999</v>
+        <v>667.28</v>
       </c>
       <c r="G403" s="11" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>1912.81</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>2027.1</v>
+        <v>2026.9</v>
       </c>
       <c r="G404" s="11" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>1205.04</v>
       </c>
       <c r="F405" s="10" t="n">
-        <v>1235.32</v>
+        <v>1234.74</v>
       </c>
       <c r="G405" s="11" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>566.55</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>573.52</v>
+        <v>574.28</v>
       </c>
       <c r="G406" s="11" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>769.35</v>
       </c>
       <c r="F407" s="10" t="n">
-        <v>858.97</v>
+        <v>858.42</v>
       </c>
       <c r="G407" s="11" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>2750.43</v>
       </c>
       <c r="F408" s="10" t="n">
-        <v>2604.9</v>
+        <v>2604.53</v>
       </c>
       <c r="G408" s="11" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>273.47</v>
       </c>
       <c r="F409" s="10" t="n">
-        <v>238.87</v>
+        <v>238.96</v>
       </c>
       <c r="G409" s="11" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>190.73</v>
       </c>
       <c r="F410" s="10" t="n">
-        <v>184.63</v>
+        <v>184.49</v>
       </c>
       <c r="G410" s="11" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>270.57</v>
       </c>
       <c r="F411" s="10" t="n">
-        <v>303.92</v>
+        <v>303.49</v>
       </c>
       <c r="G411" s="11" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>1103.8</v>
       </c>
       <c r="F413" s="10" t="n">
-        <v>1048.13</v>
+        <v>1050.2</v>
       </c>
       <c r="G413" s="11" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>995.74</v>
       </c>
       <c r="F414" s="10" t="n">
-        <v>1088.89</v>
+        <v>1088.71</v>
       </c>
       <c r="G414" s="11" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>479.92</v>
       </c>
       <c r="F415" s="10" t="n">
-        <v>497.02</v>
+        <v>496.63</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>385.85</v>
       </c>
       <c r="F416" s="10" t="n">
-        <v>428.68</v>
+        <v>429.42</v>
       </c>
       <c r="G416" s="11" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>83.18000000000001</v>
       </c>
       <c r="F417" s="10" t="n">
-        <v>99.88</v>
+        <v>100.18</v>
       </c>
       <c r="G417" s="11" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>596.13</v>
       </c>
       <c r="F418" s="10" t="n">
-        <v>595.08</v>
+        <v>596.13</v>
       </c>
       <c r="G418" s="11" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>660.55</v>
       </c>
       <c r="F419" s="10" t="n">
-        <v>580.49</v>
+        <v>581.1799999999999</v>
       </c>
       <c r="G419" s="11" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>494.83</v>
       </c>
       <c r="F420" s="10" t="n">
-        <v>451.91</v>
+        <v>451.78</v>
       </c>
       <c r="G420" s="11" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>280.98</v>
       </c>
       <c r="F421" s="10" t="n">
-        <v>245.91</v>
+        <v>245.75</v>
       </c>
       <c r="G421" s="11" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>137.43</v>
       </c>
       <c r="F422" s="10" t="n">
-        <v>151.61</v>
+        <v>151.49</v>
       </c>
       <c r="G422" s="11" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>780.35</v>
       </c>
       <c r="F423" s="10" t="n">
-        <v>731.99</v>
+        <v>731.46</v>
       </c>
       <c r="G423" s="11" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>4505.34</v>
       </c>
       <c r="F424" s="10" t="n">
-        <v>4640.34</v>
+        <v>4644.97</v>
       </c>
       <c r="G424" s="11" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>6414.57</v>
       </c>
       <c r="F425" s="10" t="n">
-        <v>6651.94</v>
+        <v>6652.48</v>
       </c>
       <c r="G425" s="11" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>442.3</v>
       </c>
       <c r="F426" s="10" t="n">
-        <v>471.66</v>
+        <v>471.48</v>
       </c>
       <c r="G426" s="11" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>827.26</v>
       </c>
       <c r="F427" s="10" t="n">
-        <v>823.2</v>
+        <v>823.0700000000001</v>
       </c>
       <c r="G427" s="11" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>125.85</v>
       </c>
       <c r="F428" s="10" t="n">
-        <v>131.41</v>
+        <v>131.61</v>
       </c>
       <c r="G428" s="11" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>178.91</v>
       </c>
       <c r="F429" s="10" t="n">
-        <v>172.04</v>
+        <v>171.95</v>
       </c>
       <c r="G429" s="11" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>1836.65</v>
       </c>
       <c r="F430" s="10" t="n">
-        <v>1752.17</v>
+        <v>1758.8</v>
       </c>
       <c r="G430" s="11" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>4267.46</v>
       </c>
       <c r="F431" s="10" t="n">
-        <v>4614.2</v>
+        <v>4619.2</v>
       </c>
       <c r="G431" s="11" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>378.79</v>
       </c>
       <c r="F433" s="10" t="n">
-        <v>399.16</v>
+        <v>399.3</v>
       </c>
       <c r="G433" s="11" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>1259.63</v>
       </c>
       <c r="F434" s="10" t="n">
-        <v>1357.1</v>
+        <v>1358.38</v>
       </c>
       <c r="G434" s="11" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>502.42</v>
       </c>
       <c r="F435" s="10" t="n">
-        <v>469.35</v>
+        <v>469.85</v>
       </c>
       <c r="G435" s="11" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>147.87</v>
       </c>
       <c r="F436" s="10" t="n">
-        <v>161.35</v>
+        <v>161.61</v>
       </c>
       <c r="G436" s="12" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>1508.34</v>
       </c>
       <c r="F437" s="10" t="n">
-        <v>1572.47</v>
+        <v>1567.12</v>
       </c>
       <c r="G437" s="12" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>2889.5</v>
       </c>
       <c r="F438" s="10" t="n">
-        <v>3074.29</v>
+        <v>3074.6</v>
       </c>
       <c r="G438" s="11" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>734.85</v>
       </c>
       <c r="F439" s="10" t="n">
-        <v>820.8099999999999</v>
+        <v>820.4299999999999</v>
       </c>
       <c r="G439" s="11" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>649.6900000000001</v>
       </c>
       <c r="F440" s="10" t="n">
-        <v>735.8</v>
+        <v>735.75</v>
       </c>
       <c r="G440" s="11" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>807.62</v>
       </c>
       <c r="F441" s="10" t="n">
-        <v>842.61</v>
+        <v>843.12</v>
       </c>
       <c r="G441" s="11" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>234.54</v>
       </c>
       <c r="F442" s="10" t="n">
-        <v>264.36</v>
+        <v>265</v>
       </c>
       <c r="G442" s="11" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>666.6</v>
       </c>
       <c r="F443" s="10" t="n">
-        <v>678.71</v>
+        <v>679.79</v>
       </c>
       <c r="G443" s="11" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>1312.61</v>
       </c>
       <c r="F444" s="10" t="n">
-        <v>1083.91</v>
+        <v>1083.73</v>
       </c>
       <c r="G444" s="11" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>21589.18</v>
       </c>
       <c r="F445" s="10" t="n">
-        <v>18830.99</v>
+        <v>18821.18</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>1127.57</v>
       </c>
       <c r="F446" s="10" t="n">
-        <v>1116.54</v>
+        <v>1117.08</v>
       </c>
       <c r="G446" s="11" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>261.5</v>
       </c>
       <c r="F447" s="10" t="n">
-        <v>314.56</v>
+        <v>315.35</v>
       </c>
       <c r="G447" s="11" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>446.79</v>
       </c>
       <c r="F448" s="10" t="n">
-        <v>483.9</v>
+        <v>486.11</v>
       </c>
       <c r="G448" s="11" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>1382.74</v>
       </c>
       <c r="F449" s="10" t="n">
-        <v>1293.1</v>
+        <v>1292.36</v>
       </c>
       <c r="G449" s="11" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>505.38</v>
       </c>
       <c r="F450" s="10" t="n">
-        <v>512.77</v>
+        <v>512.55</v>
       </c>
       <c r="G450" s="11" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>246.36</v>
       </c>
       <c r="F451" s="10" t="n">
-        <v>262.53</v>
+        <v>262.75</v>
       </c>
       <c r="G451" s="11" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>1256.76</v>
       </c>
       <c r="F452" s="10" t="n">
-        <v>1411.06</v>
+        <v>1405.61</v>
       </c>
       <c r="G452" s="11" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>518.96</v>
       </c>
       <c r="F453" s="10" t="n">
-        <v>526.73</v>
+        <v>526.3099999999999</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>90.95999999999999</v>
       </c>
       <c r="F454" s="10" t="n">
-        <v>94.86</v>
+        <v>95.09</v>
       </c>
       <c r="G454" s="11" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>202.83</v>
       </c>
       <c r="F455" s="10" t="n">
-        <v>163.77</v>
+        <v>163.93</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20739,10 +20739,10 @@
         <v>26399.19</v>
       </c>
       <c r="E456" s="10" t="n">
-        <v>26490.09</v>
+        <v>26490.08</v>
       </c>
       <c r="F456" s="10" t="n">
-        <v>27053.03</v>
+        <v>27012.28</v>
       </c>
       <c r="G456" s="11" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>36.75</v>
       </c>
       <c r="F457" s="10" t="n">
-        <v>42.36</v>
+        <v>42.32</v>
       </c>
       <c r="G457" s="11" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>562.21</v>
       </c>
       <c r="F458" s="10" t="n">
-        <v>579.92</v>
+        <v>579.8</v>
       </c>
       <c r="G458" s="11" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>1776.11</v>
       </c>
       <c r="F459" s="10" t="n">
-        <v>1695.64</v>
+        <v>1692.79</v>
       </c>
       <c r="G459" s="11" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>780.11</v>
       </c>
       <c r="F460" s="10" t="n">
-        <v>822.99</v>
+        <v>823.45</v>
       </c>
       <c r="G460" s="11" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>1682.26</v>
       </c>
       <c r="F461" s="10" t="n">
-        <v>1670.57</v>
+        <v>1668.37</v>
       </c>
       <c r="G461" s="11" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>3183.53</v>
       </c>
       <c r="F463" s="10" t="n">
-        <v>3258.41</v>
+        <v>3256.75</v>
       </c>
       <c r="G463" s="11" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>42.55</v>
       </c>
       <c r="F464" s="10" t="n">
-        <v>42.62</v>
+        <v>42.6</v>
       </c>
       <c r="G464" s="11" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>115.64</v>
       </c>
       <c r="F465" s="10" t="n">
-        <v>135.22</v>
+        <v>135</v>
       </c>
       <c r="G465" s="11" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>30.94</v>
       </c>
       <c r="F466" s="10" t="n">
-        <v>33.06</v>
+        <v>33.05</v>
       </c>
       <c r="G466" s="11" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>337.51</v>
       </c>
       <c r="F467" s="10" t="n">
-        <v>352.11</v>
+        <v>352.06</v>
       </c>
       <c r="G467" s="11" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>4505.61</v>
       </c>
       <c r="F468" s="10" t="n">
-        <v>4458.04</v>
+        <v>4451.13</v>
       </c>
       <c r="G468" s="11" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>524.3200000000001</v>
       </c>
       <c r="F469" s="10" t="n">
-        <v>498.95</v>
+        <v>498.84</v>
       </c>
       <c r="G469" s="11" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>542.6799999999999</v>
       </c>
       <c r="F470" s="10" t="n">
-        <v>530.0700000000001</v>
+        <v>531.54</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>1451.86</v>
       </c>
       <c r="F471" s="10" t="n">
-        <v>1270.61</v>
+        <v>1271.91</v>
       </c>
       <c r="G471" s="11" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>898.71</v>
       </c>
       <c r="F472" s="10" t="n">
-        <v>959.13</v>
+        <v>960.72</v>
       </c>
       <c r="G472" s="11" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>63.56</v>
       </c>
       <c r="F473" s="10" t="n">
-        <v>71.26000000000001</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="G473" s="11" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>1029.26</v>
       </c>
       <c r="F474" s="10" t="n">
-        <v>975.63</v>
+        <v>976.4299999999999</v>
       </c>
       <c r="G474" s="11" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>344.31</v>
       </c>
       <c r="F475" s="10" t="n">
-        <v>376.64</v>
+        <v>376.55</v>
       </c>
       <c r="G475" s="11" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>601.5599999999999</v>
       </c>
       <c r="F476" s="10" t="n">
-        <v>563.5</v>
+        <v>563.54</v>
       </c>
       <c r="G476" s="11" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>207.66</v>
       </c>
       <c r="F477" s="10" t="n">
-        <v>215.78</v>
+        <v>215.24</v>
       </c>
       <c r="G477" s="11" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>396.04</v>
       </c>
       <c r="F479" s="10" t="n">
-        <v>423.9</v>
+        <v>424.07</v>
       </c>
       <c r="G479" s="11" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>329.65</v>
       </c>
       <c r="F480" s="10" t="n">
-        <v>335.49</v>
+        <v>335.33</v>
       </c>
       <c r="G480" s="11" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>3865.4</v>
       </c>
       <c r="F481" s="10" t="n">
-        <v>4307.67</v>
+        <v>4309.8</v>
       </c>
       <c r="G481" s="11" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>539.2</v>
       </c>
       <c r="F482" s="10" t="n">
-        <v>479.35</v>
+        <v>479.26</v>
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>80.08</v>
       </c>
       <c r="F483" s="10" t="n">
-        <v>80.65000000000001</v>
+        <v>80.72</v>
       </c>
       <c r="G483" s="11" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>977.41</v>
       </c>
       <c r="F484" s="10" t="n">
-        <v>979.74</v>
+        <v>979.85</v>
       </c>
       <c r="G484" s="11" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>1156.02</v>
       </c>
       <c r="F485" s="10" t="n">
-        <v>1039.6</v>
+        <v>1038.92</v>
       </c>
       <c r="G485" s="11" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>60.59</v>
       </c>
       <c r="F486" s="10" t="n">
-        <v>63.31</v>
+        <v>63.25</v>
       </c>
       <c r="G486" s="11" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>32995.63</v>
       </c>
       <c r="F487" s="10" t="n">
-        <v>32889.83</v>
+        <v>32925.63</v>
       </c>
       <c r="G487" s="11" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>186.33</v>
       </c>
       <c r="F488" s="10" t="n">
-        <v>230.38</v>
+        <v>230.2</v>
       </c>
       <c r="G488" s="11" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>23.55</v>
       </c>
       <c r="F490" s="10" t="n">
-        <v>25.01</v>
+        <v>25.02</v>
       </c>
       <c r="G490" s="11" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>2153.21</v>
       </c>
       <c r="F491" s="10" t="n">
-        <v>2270.61</v>
+        <v>2270.88</v>
       </c>
       <c r="G491" s="11" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>1297.72</v>
       </c>
       <c r="F492" s="10" t="n">
-        <v>1397.74</v>
+        <v>1392.78</v>
       </c>
       <c r="G492" s="11" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>568.4299999999999</v>
       </c>
       <c r="F493" s="10" t="n">
-        <v>633.95</v>
+        <v>633.38</v>
       </c>
       <c r="G493" s="11" t="inlineStr">
         <is>
@@ -22411,10 +22411,10 @@
         <v>4690.19</v>
       </c>
       <c r="E494" s="10" t="n">
-        <v>4823.52</v>
+        <v>4823.51</v>
       </c>
       <c r="F494" s="10" t="n">
-        <v>5153.99</v>
+        <v>5144.58</v>
       </c>
       <c r="G494" s="11" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>789.5700000000001</v>
       </c>
       <c r="F495" s="10" t="n">
-        <v>837.95</v>
+        <v>836.95</v>
       </c>
       <c r="G495" s="11" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>940.38</v>
       </c>
       <c r="F496" s="10" t="n">
-        <v>907.7</v>
+        <v>907.02</v>
       </c>
       <c r="G496" s="11" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>262.78</v>
       </c>
       <c r="F497" s="10" t="n">
-        <v>283.2</v>
+        <v>283.05</v>
       </c>
       <c r="G497" s="11" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>301.57</v>
       </c>
       <c r="F498" s="10" t="n">
-        <v>320.2</v>
+        <v>320.4</v>
       </c>
       <c r="G498" s="11" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>1424.2</v>
       </c>
       <c r="F499" s="10" t="n">
-        <v>1560.07</v>
+        <v>1559.95</v>
       </c>
       <c r="G499" s="11" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>3086.54</v>
       </c>
       <c r="F500" s="10" t="n">
-        <v>3075.65</v>
+        <v>3082.77</v>
       </c>
       <c r="G500" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 19-Oct-2026  17:22:04    |    Closing Price Date: 19-Oct-2026</t>
+          <t>Scan Run: 20-Oct-2026  15:35:38    |    Closing Price Date: 19-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>19-Oct-2026  17:22:04</t>
+          <t>20-Oct-2026  15:35:38</t>
         </is>
       </c>
     </row>
@@ -8541,17 +8541,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>16-Oct-2026</t>
+          <t>19-Oct-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>224.72</v>
+        <v>219.09</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>263.61</v>
+        <v>259.37</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>378.04</v>
+        <v>371.8</v>
       </c>
       <c r="F179" s="10" t="n">
         <v/>
